--- a/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
+++ b/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="Redirect map" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data findings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Redirect map'!$A$1:$F$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Redirect map'!$A$1:$K$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +44,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +68,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F3C6C6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C6E9EC"/>
       </patternFill>
     </fill>
@@ -73,12 +83,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6D5B8"/>
+        <fgColor rgb="00ECEFF3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FBE8C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6D5B8"/>
       </patternFill>
     </fill>
     <fill>
@@ -118,46 +133,68 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,15 +560,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:K191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="58" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -562,6 +604,31 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>16-mo Impr</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CTR %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best pos</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Revamp tier</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Reason / note</t>
         </is>
       </c>
@@ -586,7 +653,24 @@
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="n">
+        <v>18269</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>272</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>Rebuild as the cluster hub (title/H1/subhead, SoftwareApplication+Offer schema, remove meta-kw, links to all spokes).</t>
         </is>
@@ -612,7 +696,24 @@
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="n">
+        <v>16906</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Canonical pricing target. Point all WL-pricing blogs here.</t>
         </is>
@@ -638,7 +739,24 @@
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="n">
+        <v>10811</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Rebuild as partner-program hub (Reseller/OEM/Referral/Agency tiers, benefits, apply CTA).</t>
         </is>
@@ -658,13 +776,22 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>n/a (build)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>NEW integrations directory hub.</t>
         </is>
@@ -684,13 +811,22 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>n/a (build)</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>NEW canonical GoHighLevel landing page (consolidates GHL posts as spokes).</t>
         </is>
@@ -710,13 +846,22 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>n/a (build)</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>NEW AI Voice Agency Academy hub — organises the ~45 business posts into a learning path.</t>
         </is>
@@ -736,13 +881,22 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>n/a (build)</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>NEW white-label-by-industry index — links the ~25 vertical posts + their /receptionist/industries counterparts.</t>
         </is>
@@ -762,13 +916,22 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>n/a (build)</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>NEW compare &amp; alternatives index — links all vs/alternative pages, one per competitor.</t>
         </is>
@@ -788,13 +951,22 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>n/a (build)</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>NEW /reviews social-proof hub (Review schema).</t>
         </is>
@@ -814,13 +986,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -840,13 +1029,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -872,7 +1078,24 @@
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Canonical "how to start a voice AI agency" (Academy entry).</t>
         </is>
@@ -892,13 +1115,30 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -918,13 +1158,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -944,13 +1201,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="n">
+        <v>1193</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -970,13 +1244,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="n">
+        <v>2738</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -996,13 +1287,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1022,13 +1330,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1048,13 +1373,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="n">
+        <v>1554</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1074,7 +1416,7 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -1084,7 +1426,24 @@
           <t>/blogs/voice-ai-agency-business-model-canvas</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Chatbot; 301 to voice canvas.</t>
         </is>
@@ -1104,13 +1463,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="n">
+        <v>10358</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1130,13 +1506,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="n">
+        <v>712</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1156,13 +1549,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="5" t="n">
+        <v>1410</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1182,13 +1592,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="n">
+        <v>2372</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -1208,13 +1635,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="5" t="n">
+        <v>3070</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -1234,13 +1678,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -1260,13 +1721,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="n">
+        <v>406</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1286,13 +1764,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1312,13 +1807,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="n">
+        <v>1646</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1338,13 +1850,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="n">
+        <v>14929</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1364,7 +1893,7 @@
           <t>5 · Pricing &amp; economics</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -1374,7 +1903,24 @@
           <t>/blogs/voice-ai-white-label-pricing-breakdown-2026</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="5" t="n">
+        <v>16211</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>Fold into the canonical pricing guide; 301.</t>
         </is>
@@ -1400,7 +1946,24 @@
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Canonical agency-economics post.</t>
         </is>
@@ -1420,13 +1983,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1446,13 +2026,22 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune (no traffic)</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1472,13 +2061,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="5" t="n">
+        <v>4015</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1498,13 +2104,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="5" t="n">
+        <v>2432</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1524,13 +2147,30 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -1550,7 +2190,7 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -1560,7 +2200,24 @@
           <t>/blogs/top-10-white-label-voice-ai-platforms-for-agencies-2026</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="5" t="n">
+        <v>7954</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>Fold into canonical roundup; 301.</t>
         </is>
@@ -1580,7 +2237,7 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -1590,7 +2247,24 @@
           <t>/blogs/top-10-white-label-voice-ai-platforms-for-agencies-2026</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="5" t="n">
+        <v>44467</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>Chatbot-framed; 301 to voice roundup.</t>
         </is>
@@ -1610,7 +2284,7 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -1620,7 +2294,24 @@
           <t>/blogs/top-10-white-label-voice-ai-platforms-for-agencies-2026</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="5" t="n">
+        <v>12333</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>Fold into canonical roundup; 301.</t>
         </is>
@@ -1640,13 +2331,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>Distinct build-vs-buy angle; keep as canonical build-vs-buy.</t>
         </is>
@@ -1666,13 +2374,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F43" s="5" t="n">
+        <v>419</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1692,13 +2417,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F44" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1718,13 +2460,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" s="5" t="n">
+        <v>3566</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1744,13 +2503,30 @@
           <t>5 · Pricing &amp; economics</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F46" s="5" t="n">
+        <v>5172</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>Distinct "cheapest" price intent; keep, link to hub + pricing guide.</t>
         </is>
@@ -1770,13 +2546,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F47" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1796,13 +2589,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F48" s="5" t="n">
+        <v>2387</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1822,13 +2632,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F49" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1848,13 +2675,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F50" s="5" t="n">
+        <v>5189</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1874,13 +2718,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F51" s="5" t="n">
+        <v>426</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1900,13 +2761,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F52" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1926,7 +2804,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -1936,7 +2814,24 @@
           <t>/blogs/top-10-white-label-voice-ai-platforms-for-agencies-2026</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F53" s="5" t="n">
+        <v>5619</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>Fold into canonical roundup; 301.</t>
         </is>
@@ -1956,13 +2851,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F54" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1982,13 +2894,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F55" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2008,13 +2937,30 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F56" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
         <is>
           <t>Distinct how-to; keep as GHL spoke.</t>
         </is>
@@ -2034,7 +2980,7 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D57" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -2044,7 +2990,24 @@
           <t>/blogs/trillet-vs-gohighlevel-voice-ai</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F57" s="5" t="n">
+        <v>597</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
         <is>
           <t>Same intent; merge + 301.</t>
         </is>
@@ -2064,13 +3027,30 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F58" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
         <is>
           <t>Distinct angle; keep as GHL spoke.</t>
         </is>
@@ -2090,7 +3070,7 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -2100,7 +3080,24 @@
           <t>/integrations/gohighlevel</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F59" s="5" t="n">
+        <v>18923</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
         <is>
           <t>Fold into the new GHL landing page; 301.</t>
         </is>
@@ -2120,7 +3117,7 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D60" s="8" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -2130,7 +3127,24 @@
           <t>/blogs/trillet-vs-gohighlevel-voice-ai</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F60" s="5" t="n">
+        <v>2499</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
         <is>
           <t>Same intent; merge + 301.</t>
         </is>
@@ -2150,13 +3164,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F61" s="5" t="n">
+        <v>14695</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -2176,13 +3207,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F62" s="5" t="n">
+        <v>1626</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2202,7 +3250,7 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -2212,7 +3260,16 @@
           <t>/blogs/what-is-white-label-ai-receptionist</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr"/>
+      <c r="H63" s="5" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune (no traffic)</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
         <is>
           <t>Chatbot definitional; 301 to voice.</t>
         </is>
@@ -2232,13 +3289,30 @@
           <t>5 · Pricing &amp; economics</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F64" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
         <is>
           <t>Distinct cost-to-start intent; keep.</t>
         </is>
@@ -2258,7 +3332,7 @@
           <t>5 · Pricing &amp; economics</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -2268,7 +3342,24 @@
           <t>/blogs/ai-voice-agency-economics-real-numbers</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F65" s="5" t="n">
+        <v>651</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
         <is>
           <t>Same intent; merge + 301.</t>
         </is>
@@ -2288,13 +3379,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="F66" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2314,13 +3422,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D67" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F67" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2340,7 +3465,7 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -2350,7 +3475,24 @@
           <t>/blogs/white-label-voice-ai-features-checklist</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F68" s="5" t="n">
+        <v>1852</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
         <is>
           <t>Chatbot; 301 to voice features checklist.</t>
         </is>
@@ -2370,13 +3512,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D69" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F69" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2396,13 +3555,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F70" s="5" t="n">
+        <v>817</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2422,13 +3598,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D71" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="F71" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J71" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2448,7 +3641,7 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D72" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -2458,7 +3651,24 @@
           <t>/blogs/60-day-ai-voice-agency-launch-plan</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="F72" s="5" t="n">
+        <v>25911</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
         <is>
           <t>Chatbot-framed start; 301 to voice launch plan.</t>
         </is>
@@ -2478,13 +3688,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D73" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="F73" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2504,13 +3731,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D74" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F74" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2530,13 +3774,30 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D75" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="F75" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -2556,13 +3817,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D76" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="F76" s="5" t="n">
+        <v>1597</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2582,13 +3860,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="F77" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2608,13 +3903,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F78" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -2634,13 +3946,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D79" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="F79" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2660,13 +3989,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="F80" s="5" t="n">
+        <v>12748</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="J80" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2686,13 +4032,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D81" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F81" s="5" t="n">
+        <v>4697</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2712,7 +4075,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D82" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -2722,7 +4085,24 @@
           <t>/blogs/ai-voice-agency-economics-real-numbers</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="F82" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
         <is>
           <t>Same intent; merge as a section + 301.</t>
         </is>
@@ -2742,13 +4122,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="F83" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2768,7 +4165,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D84" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -2778,7 +4175,24 @@
           <t>/blogs/trillet-vs-my-ai-front-desk-comparison-2026</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F84" s="5" t="n">
+        <v>13268</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
         <is>
           <t>Duplicate; 301.</t>
         </is>
@@ -2798,7 +4212,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D85" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -2808,7 +4222,24 @@
           <t>/blogs/trillet-vs-my-ai-front-desk-comparison-2026</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="F85" s="5" t="n">
+        <v>4065</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
         <is>
           <t>Duplicate; 301.</t>
         </is>
@@ -2828,13 +4259,30 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D86" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr"/>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="F86" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -2854,13 +4302,30 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D87" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F87" s="5" t="n">
+        <v>667</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J87" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -2880,13 +4345,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D88" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="F88" s="5" t="n">
+        <v>4148</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2906,13 +4388,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D89" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="F89" s="5" t="n">
+        <v>18493</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2932,13 +4431,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D90" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="F90" s="5" t="n">
+        <v>1706</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2958,13 +4474,30 @@
           <t>5 · Pricing &amp; economics</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F91" s="5" t="n">
+        <v>690</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J91" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -2984,7 +4517,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D92" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -2994,7 +4527,24 @@
           <t>/blogs/trillet-vs-retell-vs-vapi-comparison</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="F92" s="5" t="n">
+        <v>15338</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
         <is>
           <t>301 to canonical vs.</t>
         </is>
@@ -3014,7 +4564,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D93" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -3024,7 +4574,24 @@
           <t>/blogs/trillet-vs-smith-ai-comparison-2026</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="F93" s="5" t="n">
+        <v>14244</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
         <is>
           <t>Duplicate; 301.</t>
         </is>
@@ -3044,13 +4611,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D94" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr">
+      <c r="F94" s="5" t="n">
+        <v>2625</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3070,7 +4654,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D95" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -3080,7 +4664,24 @@
           <t>/blogs/synthflow-vs-trillet-comparison</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="F95" s="5" t="n">
+        <v>8265</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
         <is>
           <t>Duplicate; 301.</t>
         </is>
@@ -3106,7 +4707,24 @@
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr">
+      <c r="F96" s="5" t="n">
+        <v>12948</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
         <is>
           <t>Canonical Synthflow page.</t>
         </is>
@@ -3126,13 +4744,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D97" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="F97" s="5" t="n">
+        <v>363</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3152,13 +4787,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D98" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="F98" s="5" t="n">
+        <v>477</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3178,13 +4830,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D99" s="9" t="inlineStr">
+      <c r="D99" s="14" t="inlineStr">
         <is>
           <t>REVAMP</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F99" s="5" t="n">
+        <v>35959</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
         <is>
           <t>Canonical "best white-label voice AI" roundup. Rewrite as honest named comparison + current data.</t>
         </is>
@@ -3204,13 +4873,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="D100" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="F100" s="5" t="n">
+        <v>6702</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="J100" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3230,13 +4916,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D101" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="F101" s="5" t="n">
+        <v>12431</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3262,7 +4965,24 @@
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr">
+      <c r="F102" s="5" t="n">
+        <v>789</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
         <is>
           <t>Canonical "GHL native vs Trillet" comparison.</t>
         </is>
@@ -3282,13 +5002,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="D103" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr"/>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="F103" s="5" t="n">
+        <v>3257</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3308,13 +5045,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D104" s="6" t="inlineStr">
+      <c r="D104" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr"/>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="F104" s="5" t="n">
+        <v>12186</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3340,7 +5094,24 @@
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr"/>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="F105" s="5" t="n">
+        <v>6286</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K105" s="4" t="inlineStr">
         <is>
           <t>Canonical My AI Front Desk page.</t>
         </is>
@@ -3366,7 +5137,24 @@
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr"/>
-      <c r="F106" s="4" t="inlineStr">
+      <c r="F106" s="5" t="n">
+        <v>8596</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
         <is>
           <t>Canonical Retell/Vapi comparison.</t>
         </is>
@@ -3386,13 +5174,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D107" s="6" t="inlineStr">
+      <c r="D107" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr"/>
-      <c r="F107" s="4" t="inlineStr">
+      <c r="F107" s="5" t="n">
+        <v>3480</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3418,7 +5223,24 @@
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr"/>
-      <c r="F108" s="4" t="inlineStr">
+      <c r="F108" s="5" t="n">
+        <v>8420</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
         <is>
           <t>Canonical Smith.ai page.</t>
         </is>
@@ -3438,13 +5260,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D109" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr">
+      <c r="F109" s="5" t="n">
+        <v>1392</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3464,7 +5303,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D110" s="7" t="inlineStr">
+      <c r="D110" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -3474,7 +5313,24 @@
           <t>/blogs/trillet-vs-retell-vs-vapi-comparison</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr">
+      <c r="F110" s="5" t="n">
+        <v>3834</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
         <is>
           <t>Thin agency-alt; 301 to canonical vs.</t>
         </is>
@@ -3494,13 +5350,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
+      <c r="D111" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr">
+      <c r="F111" s="5" t="n">
+        <v>838</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
         <is>
           <t>Distinct compliance angle (the wedge); keep.</t>
         </is>
@@ -3520,13 +5393,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D112" s="6" t="inlineStr">
+      <c r="D112" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr">
+      <c r="F112" s="5" t="n">
+        <v>5279</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
         <is>
           <t>Distinct: Vapi own WL options; keep.</t>
         </is>
@@ -3546,13 +5436,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="D113" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr"/>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="F113" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J113" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3572,13 +5479,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="D114" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr"/>
-      <c r="F114" s="4" t="inlineStr">
+      <c r="F114" s="5" t="n">
+        <v>478</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3598,13 +5522,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr">
+      <c r="D115" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr"/>
-      <c r="F115" s="4" t="inlineStr">
+      <c r="F115" s="5" t="n">
+        <v>11332</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -3624,13 +5565,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="D116" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr"/>
-      <c r="F116" s="4" t="inlineStr">
+      <c r="F116" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -3650,13 +5608,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D117" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr">
+      <c r="F117" s="5" t="n">
+        <v>1875</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -3676,13 +5651,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D118" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr">
+      <c r="F118" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K118" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -3702,13 +5694,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="D119" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr"/>
-      <c r="F119" s="4" t="inlineStr">
+      <c r="F119" s="5" t="n">
+        <v>539</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J119" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -3728,13 +5737,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D120" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="F120" s="5" t="n">
+        <v>3191</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J120" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3754,13 +5780,22 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D121" s="10" t="inlineStr">
+      <c r="D121" s="15" t="inlineStr">
         <is>
           <t>REFRAME</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr">
+      <c r="F121" s="5" t="inlineStr"/>
+      <c r="G121" s="5" t="inlineStr"/>
+      <c r="H121" s="5" t="inlineStr"/>
+      <c r="I121" s="5" t="inlineStr"/>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune (no traffic)</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
         <is>
           <t>KEEP but sharpen "sell voice, not chat"; the chatbot-&gt;voice converter.</t>
         </is>
@@ -3780,13 +5815,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D122" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr"/>
-      <c r="F122" s="4" t="inlineStr">
+      <c r="F122" s="5" t="n">
+        <v>486</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J122" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -3806,13 +5858,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D123" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr"/>
-      <c r="F123" s="4" t="inlineStr">
+      <c r="F123" s="5" t="n">
+        <v>3654</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3832,13 +5901,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D124" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr"/>
-      <c r="F124" s="4" t="inlineStr">
+      <c r="F124" s="5" t="n">
+        <v>2061</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J124" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3858,13 +5944,30 @@
           <t>5 · Pricing &amp; economics</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D125" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr"/>
-      <c r="F125" s="4" t="inlineStr">
+      <c r="F125" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K125" s="4" t="inlineStr">
         <is>
           <t>Distinct ROI tool; keep.</t>
         </is>
@@ -3884,7 +5987,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D126" s="8" t="inlineStr">
+      <c r="D126" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -3894,7 +5997,16 @@
           <t>/blogs/voice-ai-wrapper-vs-native-platform</t>
         </is>
       </c>
-      <c r="F126" s="4" t="inlineStr">
+      <c r="F126" s="5" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr"/>
+      <c r="H126" s="5" t="inlineStr"/>
+      <c r="I126" s="5" t="inlineStr"/>
+      <c r="J126" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune (no traffic)</t>
+        </is>
+      </c>
+      <c r="K126" s="4" t="inlineStr">
         <is>
           <t>Merge + 301.</t>
         </is>
@@ -3914,13 +6026,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="D127" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr"/>
-      <c r="F127" s="4" t="inlineStr">
+      <c r="F127" s="5" t="n">
+        <v>271</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3940,13 +6069,22 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D128" s="6" t="inlineStr">
+      <c r="D128" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr"/>
-      <c r="F128" s="4" t="inlineStr">
+      <c r="F128" s="5" t="inlineStr"/>
+      <c r="G128" s="5" t="inlineStr"/>
+      <c r="H128" s="5" t="inlineStr"/>
+      <c r="I128" s="5" t="inlineStr"/>
+      <c r="J128" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune (no traffic)</t>
+        </is>
+      </c>
+      <c r="K128" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3966,13 +6104,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="D129" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr"/>
-      <c r="F129" s="4" t="inlineStr">
+      <c r="F129" s="5" t="n">
+        <v>353</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J129" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K129" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -3992,13 +6147,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D130" s="6" t="inlineStr">
+      <c r="D130" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="4" t="inlineStr">
+      <c r="F130" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="J130" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K130" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -4018,13 +6190,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D131" s="6" t="inlineStr">
+      <c r="D131" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr"/>
-      <c r="F131" s="4" t="inlineStr">
+      <c r="F131" s="5" t="n">
+        <v>6173</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J131" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -4044,13 +6233,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D132" s="6" t="inlineStr">
+      <c r="D132" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr"/>
-      <c r="F132" s="4" t="inlineStr">
+      <c r="F132" s="5" t="n">
+        <v>2613</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -4070,13 +6276,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="D133" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr"/>
-      <c r="F133" s="4" t="inlineStr">
+      <c r="F133" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J133" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -4096,13 +6319,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="D134" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr"/>
-      <c r="F134" s="4" t="inlineStr">
+      <c r="F134" s="5" t="n">
+        <v>397</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J134" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K134" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -4122,13 +6362,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D135" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr"/>
-      <c r="F135" s="4" t="inlineStr">
+      <c r="F135" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J135" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -4148,13 +6405,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="D136" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr"/>
-      <c r="F136" s="4" t="inlineStr">
+      <c r="F136" s="5" t="n">
+        <v>480</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="J136" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -4174,13 +6448,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D137" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr"/>
-      <c r="F137" s="4" t="inlineStr">
+      <c r="F137" s="5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K137" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -4200,13 +6491,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="D138" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr"/>
-      <c r="F138" s="4" t="inlineStr">
+      <c r="F138" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J138" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K138" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -4226,13 +6534,30 @@
           <t>5 · Pricing &amp; economics</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
+      <c r="D139" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr"/>
-      <c r="F139" s="4" t="inlineStr">
+      <c r="F139" s="5" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J139" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K139" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -4252,13 +6577,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr">
+      <c r="D140" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr"/>
-      <c r="F140" s="4" t="inlineStr">
+      <c r="F140" s="5" t="n">
+        <v>2581</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J140" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4278,13 +6620,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="D141" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr"/>
-      <c r="F141" s="4" t="inlineStr">
+      <c r="F141" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J141" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -4304,13 +6663,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="D142" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr"/>
-      <c r="F142" s="4" t="inlineStr">
+      <c r="F142" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J142" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K142" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -4330,13 +6706,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="D143" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr"/>
-      <c r="F143" s="4" t="inlineStr">
+      <c r="F143" s="5" t="n">
+        <v>1536</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J143" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -4356,13 +6749,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="D144" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr"/>
-      <c r="F144" s="4" t="inlineStr">
+      <c r="F144" s="5" t="n">
+        <v>3221</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4382,7 +6792,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D145" s="8" t="inlineStr">
+      <c r="D145" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -4392,7 +6802,24 @@
           <t>/blogs/voice-first-vs-chat-first-platforms</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr">
+      <c r="F145" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J145" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
         <is>
           <t>Merge + 301.</t>
         </is>
@@ -4412,7 +6839,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D146" s="8" t="inlineStr">
+      <c r="D146" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -4422,7 +6849,24 @@
           <t>/blogs/voice-first-vs-chat-first-platforms</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr">
+      <c r="F146" s="5" t="n">
+        <v>8335</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J146" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
         <is>
           <t>Merge + 301.</t>
         </is>
@@ -4442,13 +6886,30 @@
           <t>5 · Pricing &amp; economics</t>
         </is>
       </c>
-      <c r="D147" s="9" t="inlineStr">
+      <c r="D147" s="14" t="inlineStr">
         <is>
           <t>REVAMP</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr"/>
-      <c r="F147" s="4" t="inlineStr">
+      <c r="F147" s="5" t="n">
+        <v>47431</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J147" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
         <is>
           <t>Canonical WL-pricing GUIDE. 46k impressions @0.06% CTR — rewrite title/meta/snippet, add table + CTA to /whitelabel/pricing.</t>
         </is>
@@ -4474,7 +6935,24 @@
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr">
+      <c r="F148" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J148" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
         <is>
           <t>Canonical wrapper-vs-native (the "we own the stack" differentiator).</t>
         </is>
@@ -4500,7 +6978,24 @@
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr"/>
-      <c r="F149" s="4" t="inlineStr">
+      <c r="F149" s="5" t="n">
+        <v>2149</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J149" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
         <is>
           <t>Canonical voice-vs-text positioning post.</t>
         </is>
@@ -4520,13 +7015,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D150" s="6" t="inlineStr">
+      <c r="D150" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr"/>
-      <c r="F150" s="4" t="inlineStr">
+      <c r="F150" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H150" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J150" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4546,13 +7058,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D151" s="6" t="inlineStr">
+      <c r="D151" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr"/>
-      <c r="F151" s="4" t="inlineStr">
+      <c r="F151" s="5" t="n">
+        <v>1815</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J151" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4572,13 +7101,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D152" s="6" t="inlineStr">
+      <c r="D152" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr"/>
-      <c r="F152" s="4" t="inlineStr">
+      <c r="F152" s="5" t="n">
+        <v>2743</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I152" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J152" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4598,13 +7144,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D153" s="6" t="inlineStr">
+      <c r="D153" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr"/>
-      <c r="F153" s="4" t="inlineStr">
+      <c r="F153" s="5" t="n">
+        <v>26793</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J153" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4624,13 +7187,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D154" s="6" t="inlineStr">
+      <c r="D154" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr"/>
-      <c r="F154" s="4" t="inlineStr">
+      <c r="F154" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J154" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K154" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4650,7 +7230,7 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D155" s="7" t="inlineStr">
+      <c r="D155" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -4660,7 +7240,24 @@
           <t>/blogs/what-is-white-label-ai-receptionist</t>
         </is>
       </c>
-      <c r="F155" s="4" t="inlineStr">
+      <c r="F155" s="5" t="n">
+        <v>17258</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J155" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
         <is>
           <t>Chatbot definitional; 301 to voice.</t>
         </is>
@@ -4680,13 +7277,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D156" s="6" t="inlineStr">
+      <c r="D156" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr"/>
-      <c r="F156" s="4" t="inlineStr">
+      <c r="F156" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J156" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -4706,13 +7320,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D157" s="6" t="inlineStr">
+      <c r="D157" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr"/>
-      <c r="F157" s="4" t="inlineStr">
+      <c r="F157" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J157" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -4732,13 +7363,30 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D158" s="6" t="inlineStr">
+      <c r="D158" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr"/>
-      <c r="F158" s="4" t="inlineStr">
+      <c r="F158" s="5" t="n">
+        <v>4903</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J158" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K158" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -4758,13 +7406,30 @@
           <t>6 · Integrations</t>
         </is>
       </c>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="D159" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr"/>
-      <c r="F159" s="4" t="inlineStr">
+      <c r="F159" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J159" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K159" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -4784,7 +7449,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D160" s="7" t="inlineStr">
+      <c r="D160" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -4794,7 +7459,24 @@
           <t>/blogs/voice-ai-white-label-pricing-breakdown-2026</t>
         </is>
       </c>
-      <c r="F160" s="4" t="inlineStr">
+      <c r="F160" s="5" t="n">
+        <v>14823</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I160" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J160" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
         <is>
           <t>Chatbot-framed; 301 to voice pricing guide.</t>
         </is>
@@ -4814,7 +7496,7 @@
           <t>5 · Pricing &amp; economics</t>
         </is>
       </c>
-      <c r="D161" s="8" t="inlineStr">
+      <c r="D161" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -4824,7 +7506,24 @@
           <t>/blogs/voice-ai-agency-roi-model</t>
         </is>
       </c>
-      <c r="F161" s="4" t="inlineStr">
+      <c r="F161" s="5" t="n">
+        <v>4804</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I161" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J161" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K161" s="4" t="inlineStr">
         <is>
           <t>Merge tool into voice ROI model; 301.</t>
         </is>
@@ -4844,13 +7543,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="D162" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr"/>
-      <c r="F162" s="4" t="inlineStr">
+      <c r="F162" s="5" t="n">
+        <v>1403</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J162" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K162" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -4870,13 +7586,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="D163" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr"/>
-      <c r="F163" s="4" t="inlineStr">
+      <c r="F163" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J163" s="10" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -4896,13 +7629,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D164" s="6" t="inlineStr">
+      <c r="D164" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr"/>
-      <c r="F164" s="4" t="inlineStr">
+      <c r="F164" s="5" t="n">
+        <v>2938</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J164" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -4922,13 +7672,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D165" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr"/>
-      <c r="F165" s="4" t="inlineStr">
+      <c r="F165" s="5" t="n">
+        <v>6011</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H165" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J165" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K165" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -4948,13 +7715,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D166" s="6" t="inlineStr">
+      <c r="D166" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr"/>
-      <c r="F166" s="4" t="inlineStr">
+      <c r="F166" s="5" t="n">
+        <v>498</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I166" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J166" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K166" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -4974,13 +7758,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D167" s="6" t="inlineStr">
+      <c r="D167" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr"/>
-      <c r="F167" s="4" t="inlineStr">
+      <c r="F167" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J167" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K167" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -5000,13 +7801,30 @@
           <t>3 · By industry</t>
         </is>
       </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="D168" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr"/>
-      <c r="F168" s="4" t="inlineStr">
+      <c r="F168" s="5" t="n">
+        <v>2421</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H168" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J168" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K168" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -5026,13 +7844,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D169" s="6" t="inlineStr">
+      <c r="D169" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr"/>
-      <c r="F169" s="4" t="inlineStr">
+      <c r="F169" s="5" t="n">
+        <v>2598</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J169" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K169" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5052,7 +7887,7 @@
           <t>5 · Pricing &amp; economics</t>
         </is>
       </c>
-      <c r="D170" s="8" t="inlineStr">
+      <c r="D170" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -5062,7 +7897,24 @@
           <t>/blogs/white-label-ai-profit-margins</t>
         </is>
       </c>
-      <c r="F170" s="4" t="inlineStr">
+      <c r="F170" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J170" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K170" s="4" t="inlineStr">
         <is>
           <t>Near-duplicate; merge + 301.</t>
         </is>
@@ -5088,7 +7940,24 @@
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr"/>
-      <c r="F171" s="4" t="inlineStr">
+      <c r="F171" s="5" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J171" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K171" s="4" t="inlineStr">
         <is>
           <t>Canonical profit-margins post.</t>
         </is>
@@ -5108,13 +7977,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="D172" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr"/>
-      <c r="F172" s="4" t="inlineStr">
+      <c r="F172" s="5" t="n">
+        <v>1038</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J172" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K172" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5134,13 +8020,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D173" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr"/>
-      <c r="F173" s="4" t="inlineStr">
+      <c r="F173" s="5" t="n">
+        <v>1429</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J173" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K173" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5160,13 +8063,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D174" s="6" t="inlineStr">
+      <c r="D174" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr"/>
-      <c r="F174" s="4" t="inlineStr">
+      <c r="F174" s="5" t="n">
+        <v>3483</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H174" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J174" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K174" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5186,13 +8106,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D175" s="6" t="inlineStr">
+      <c r="D175" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr"/>
-      <c r="F175" s="4" t="inlineStr">
+      <c r="F175" s="5" t="n">
+        <v>7029</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H175" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J175" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K175" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5212,13 +8149,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D176" s="6" t="inlineStr">
+      <c r="D176" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr"/>
-      <c r="F176" s="4" t="inlineStr">
+      <c r="F176" s="5" t="n">
+        <v>4806</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H176" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I176" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J176" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K176" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5238,13 +8192,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="D177" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr"/>
-      <c r="F177" s="4" t="inlineStr">
+      <c r="F177" s="5" t="n">
+        <v>738</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H177" s="5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I177" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J177" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K177" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5264,13 +8235,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D178" s="6" t="inlineStr">
+      <c r="D178" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr"/>
-      <c r="F178" s="4" t="inlineStr">
+      <c r="F178" s="5" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H178" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I178" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J178" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K178" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5290,7 +8278,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D179" s="7" t="inlineStr">
+      <c r="D179" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -5300,7 +8288,24 @@
           <t>/whitelabel</t>
         </is>
       </c>
-      <c r="F179" s="4" t="inlineStr">
+      <c r="F179" s="5" t="n">
+        <v>4750</v>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H179" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I179" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J179" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K179" s="4" t="inlineStr">
         <is>
           <t>Off-topic (chatgpt); 301 to hub.</t>
         </is>
@@ -5320,13 +8325,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D180" s="6" t="inlineStr">
+      <c r="D180" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr"/>
-      <c r="F180" s="4" t="inlineStr">
+      <c r="F180" s="5" t="n">
+        <v>4831</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J180" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K180" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5346,13 +8368,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="D181" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr"/>
-      <c r="F181" s="4" t="inlineStr">
+      <c r="F181" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J181" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K181" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5372,13 +8411,30 @@
           <t>5 · Pricing &amp; economics</t>
         </is>
       </c>
-      <c r="D182" s="6" t="inlineStr">
+      <c r="D182" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr"/>
-      <c r="F182" s="4" t="inlineStr">
+      <c r="F182" s="5" t="n">
+        <v>6540</v>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I182" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J182" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K182" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5398,13 +8454,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D183" s="6" t="inlineStr">
+      <c r="D183" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr"/>
-      <c r="F183" s="4" t="inlineStr">
+      <c r="F183" s="5" t="n">
+        <v>9907</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="H183" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I183" s="5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J183" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K183" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5424,7 +8497,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D184" s="8" t="inlineStr">
+      <c r="D184" s="13" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -5434,7 +8507,24 @@
           <t>/blogs/voice-ai-wrapper-vs-native-platform</t>
         </is>
       </c>
-      <c r="F184" s="4" t="inlineStr">
+      <c r="F184" s="5" t="n">
+        <v>949</v>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I184" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J184" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K184" s="4" t="inlineStr">
         <is>
           <t>Merge + 301.</t>
         </is>
@@ -5454,7 +8544,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D185" s="7" t="inlineStr">
+      <c r="D185" s="12" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -5464,7 +8554,24 @@
           <t>/blogs/build-on-vapi-retell-vs-buy-white-label</t>
         </is>
       </c>
-      <c r="F185" s="4" t="inlineStr">
+      <c r="F185" s="5" t="n">
+        <v>1782</v>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I185" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J185" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K185" s="4" t="inlineStr">
         <is>
           <t>Chatbot build-vs-buy; 301 to canonical build-vs-buy.</t>
         </is>
@@ -5484,13 +8591,30 @@
           <t>1 · Platform (money)</t>
         </is>
       </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="D186" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr"/>
-      <c r="F186" s="4" t="inlineStr">
+      <c r="F186" s="5" t="n">
+        <v>1296</v>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H186" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I186" s="5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="J186" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K186" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5510,13 +8634,30 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="D187" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr"/>
-      <c r="F187" s="4" t="inlineStr">
+      <c r="F187" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" s="5" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="J187" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K187" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -5536,13 +8677,30 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="D188" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr"/>
-      <c r="F188" s="4" t="inlineStr">
+      <c r="F188" s="5" t="n">
+        <v>711</v>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J188" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K188" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5562,13 +8720,30 @@
           <t>0 · Partnerships</t>
         </is>
       </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="D189" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr"/>
-      <c r="F189" s="4" t="inlineStr">
+      <c r="F189" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J189" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K189" s="4" t="inlineStr">
         <is>
           <t>Revamp under the program hub.</t>
         </is>
@@ -5588,13 +8763,30 @@
           <t>0 · Partnerships</t>
         </is>
       </c>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="D190" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr"/>
-      <c r="F190" s="4" t="inlineStr">
+      <c r="F190" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J190" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K190" s="4" t="inlineStr">
         <is>
           <t>Revamp; link from voice-ai-agency-referral-program.</t>
         </is>
@@ -5614,20 +8806,37 @@
           <t>0 · Partnerships</t>
         </is>
       </c>
-      <c r="D191" s="6" t="inlineStr">
+      <c r="D191" s="9" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr"/>
-      <c r="F191" s="4" t="inlineStr">
+      <c r="F191" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J191" s="11" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="K191" s="4" t="inlineStr">
         <is>
           <t>Revamp under the program hub; wire Academy posts to it.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F191"/>
+  <autoFilter ref="A1:K191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5638,27 +8847,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -5668,7 +8877,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>CANONICAL</t>
         </is>
@@ -5678,7 +8887,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>REVAMP</t>
         </is>
@@ -5688,7 +8897,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
@@ -5698,7 +8907,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -5708,7 +8917,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
@@ -5718,7 +8927,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>REFRAME</t>
         </is>
@@ -5728,12 +8937,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
@@ -5807,6 +9016,230 @@
       </c>
       <c r="B17" t="n">
         <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Revamp tier (GSC-grounded)</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B · light revamp</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C · interlink/prune</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C · interlink/prune (no traffic)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>n/a (build)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>16 months (2025-05-07 to 2026-09-06), Web search</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Site total</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>18,848 clicks · 1,908,737 impressions · 0.99% CTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>Impressions grew ~46x as programmatic content shipped (13.5k -&gt; 621k per 90 days); clicks only ~1.8x; CTR fell 19.85% -&gt; 0.76%. Relevance/snippet failure at scale, confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Apex vs www</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>www 1,365,616 impr @0.94% CTR; apex 1,027,877 impr @0.64%. 87 of 179 white-label paths appear on BOTH hosts, splitting 677,654 impressions. Biggest single lever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>WL cluster</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>764,907 impressions = 40% of all site impressions, but only 2,036 clicks @ 0.27% CTR (vs 0.99% site).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>Revamp prize</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>93 WL pages sit in striking distance (pos&lt;=20, impr&gt;=1000, CTR&lt;1.5%) holding ~721,000 impressions — the Tier-A revamp target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>Chatbot = wasted impressions</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>'white label chatbot' 1,569 impr pos 18.9 0.13%; 'chatbot white label' 1,354; 'white label ai chatbot' 1,003; 'whitelabel chatbot' 939; all ~0% CTR. Voice-first Trillet can't convert chatbot demand — reframe/redirect confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Voice/receptionist converts</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>'white label ai receptionist' 1,549 impr, 37 clk, 2.39% CTR (best non-brand); 'ai receptionist white label' 1.59%; 'retell ai white label' 3.35%. 10-20x better than chatbot terms at similar positions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Head terms stuck</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>'white label ai voice agent' pos 26.8; 'white label ai platform' pos 30.6; 'white label voice' pos 19.7 — the terms the /whitelabel hub must win are on page 2-3 today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Brand WL demand</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>'trillet white label' 46.73% CTR; 'trillet ai white label' 21.70%. Real branded white-label demand exists and converts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Worst offenders (page)</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>voice-ai-white-label-pricing-breakdown-2026 42,150 impr @0.06%; best-white-label-ai-chatbot 39,390 @0.19%; voicify-alternative 26,793 impr @0.00% (1 click).</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
+++ b/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
@@ -9142,19 +9142,19 @@
       </c>
       <c r="B4" s="26" t="inlineStr">
         <is>
-          <t>Impressions grew ~46x as programmatic content shipped (13.5k -&gt; 621k per 90 days); clicks only ~1.8x; CTR fell 19.85% -&gt; 0.76%. Relevance/snippet failure at scale, confirmed.</t>
+          <t>Impressions grew ~46x as programmatic content shipped (13.5k -&gt; 621k per 90 days); clicks only ~1.8x; CTR fell 19.85% -&gt; 0.76%. Relevance/snippet failure at scale, confirmed — this (not host duplication) is now the primary problem.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>Apex vs www</t>
+          <t>Apex/www — RESOLVED</t>
         </is>
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>www 1,365,616 impr @0.94% CTR; apex 1,027,877 impr @0.64%. 87 of 179 white-label paths appear on BOTH hosts, splitting 677,654 impressions. Biggest single lever.</t>
+          <t>Host duplication has been canonicalised to a single host (no longer a lever). The 16-mo export still shows both hosts historically; tiers here are deduped by path, i.e. the consolidated single-URL view. Re-pull GSC in 4-8 weeks to measure the consolidation lift.</t>
         </is>
       </c>
     </row>
@@ -9173,12 +9173,12 @@
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>Revamp prize</t>
+          <t>Revamp prize (#1 lever now)</t>
         </is>
       </c>
       <c r="B7" s="26" t="inlineStr">
         <is>
-          <t>93 WL pages sit in striking distance (pos&lt;=20, impr&gt;=1000, CTR&lt;1.5%) holding ~721,000 impressions — the Tier-A revamp target.</t>
+          <t>93 WL pages sit in striking distance (pos&lt;=20, impr&gt;=1000, CTR&lt;1.5%) holding ~721,000 impressions — the Tier-A revamp target and, with apex/www done, the single biggest lever. Note: exclude chatbot-query impressions (structurally unconvertible for a voice product) from any CTR-lift forecast.</t>
         </is>
       </c>
     </row>

--- a/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
+++ b/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
@@ -4165,16 +4165,12 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D84" s="12" t="inlineStr">
-        <is>
-          <t>REDIRECT</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>/blogs/trillet-vs-my-ai-front-desk-comparison-2026</t>
-        </is>
-      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="5" t="n">
         <v>13268</v>
       </c>
@@ -4194,7 +4190,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Duplicate; 301.</t>
+          <t>SERP-validated (keep): ranks #2 for "my ai front desk alternative" — distinct intent from the vs.</t>
         </is>
       </c>
     </row>
@@ -4212,16 +4208,12 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t>REDIRECT</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>/blogs/trillet-vs-my-ai-front-desk-comparison-2026</t>
-        </is>
-      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr"/>
       <c r="F85" s="5" t="n">
         <v>4065</v>
       </c>
@@ -4241,7 +4233,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Duplicate; 301.</t>
+          <t>SERP-validated (keep): distinct white-label angle; differentiate from alternative-2026 (general) and the vs (head-to-head).</t>
         </is>
       </c>
     </row>
@@ -4517,16 +4509,12 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D92" s="12" t="inlineStr">
-        <is>
-          <t>REDIRECT</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>/blogs/trillet-vs-retell-vs-vapi-comparison</t>
-        </is>
-      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr"/>
       <c r="F92" s="5" t="n">
         <v>15338</v>
       </c>
@@ -4546,7 +4534,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>301 to canonical vs.</t>
+          <t>SERP-validated (keep): owns the converting "retell ai white label" niche (3.35% CTR); distinct intent from the head-to-head vs.</t>
         </is>
       </c>
     </row>
@@ -4564,16 +4552,12 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>REDIRECT</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>/blogs/trillet-vs-smith-ai-comparison-2026</t>
-        </is>
-      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr"/>
       <c r="F93" s="5" t="n">
         <v>14244</v>
       </c>
@@ -4593,7 +4577,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Duplicate; 301.</t>
+          <t>SERP-validated (keep): "smith ai alternative" is roundup intent, distinct from the head-to-head vs.</t>
         </is>
       </c>
     </row>
@@ -4654,16 +4638,12 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D95" s="12" t="inlineStr">
-        <is>
-          <t>REDIRECT</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>/blogs/synthflow-vs-trillet-comparison</t>
-        </is>
-      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr"/>
       <c r="F95" s="5" t="n">
         <v>8265</v>
       </c>
@@ -4683,7 +4663,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Duplicate; 301.</t>
+          <t>SERP-validated (keep): distinct agency-angle content; co-ranks only on the brand term. Differentiate from the vs.</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4706,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Canonical Synthflow page.</t>
+          <t>Canonical head-to-head. synthflow-alternative-for-agencies has distinct content and is KEPT (SERP-validated).</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5093,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Canonical My AI Front Desk page.</t>
+          <t>Canonical head-to-head. The two MAFD alternative pages serve different intent and are KEPT (SERP-validated), not merged here.</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5136,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Canonical Retell/Vapi comparison.</t>
+          <t>Canonical head-to-head. The Retell/Vapi white-label "alternative" pages own distinct intent and are KEPT (SERP-validated).</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5222,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Canonical Smith.ai page.</t>
+          <t>Canonical head-to-head. smith-ai-alternative-2026 owns roundup intent and is KEPT (SERP-validated).</t>
         </is>
       </c>
     </row>
@@ -5303,16 +5283,12 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D110" s="12" t="inlineStr">
-        <is>
-          <t>REDIRECT</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>/blogs/trillet-vs-retell-vs-vapi-comparison</t>
-        </is>
-      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr"/>
       <c r="F110" s="5" t="n">
         <v>3834</v>
       </c>
@@ -5332,7 +5308,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>Thin agency-alt; 301 to canonical vs.</t>
+          <t>SERP-validated (keep): ranks p1 (#3) for "vapi alternative for agencies" — roundup intent, distinct from the vs.</t>
         </is>
       </c>
     </row>
@@ -8903,7 +8879,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6">
@@ -8923,7 +8899,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">

--- a/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
+++ b/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Data findings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Redirect map'!$A$1:$K$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Redirect map'!$A$1:$M$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,12 +98,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE0FB"/>
+        <fgColor rgb="00E4D4F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E4D4F0"/>
+        <fgColor rgb="00CFE0FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -183,11 +183,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K191"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,9 @@
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="58" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="58" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -629,6 +631,16 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Overlap %</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Overlap verdict</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Reason / note</t>
         </is>
       </c>
@@ -670,7 +682,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>Rebuild as the cluster hub (title/H1/subhead, SoftwareApplication+Offer schema, remove meta-kw, links to all spokes).</t>
         </is>
@@ -713,7 +727,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>Canonical pricing target. Point all WL-pricing blogs here.</t>
         </is>
@@ -756,7 +772,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Rebuild as partner-program hub (Reseller/OEM/Referral/Agency tiers, benefits, apply CTA).</t>
         </is>
@@ -791,7 +809,9 @@
           <t>n/a (build)</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>NEW integrations directory hub.</t>
         </is>
@@ -826,7 +846,9 @@
           <t>n/a (build)</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>NEW canonical GoHighLevel landing page (consolidates GHL posts as spokes).</t>
         </is>
@@ -861,7 +883,9 @@
           <t>n/a (build)</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>NEW AI Voice Agency Academy hub — organises the ~45 business posts into a learning path.</t>
         </is>
@@ -896,7 +920,9 @@
           <t>n/a (build)</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>NEW white-label-by-industry index — links the ~25 vertical posts + their /receptionist/industries counterparts.</t>
         </is>
@@ -931,7 +957,9 @@
           <t>n/a (build)</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>NEW compare &amp; alternatives index — links all vs/alternative pages, one per competitor.</t>
         </is>
@@ -966,7 +994,9 @@
           <t>n/a (build)</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>NEW /reviews social-proof hub (Review schema).</t>
         </is>
@@ -1009,7 +1039,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1052,7 +1084,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1072,9 +1106,9 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>CANONICAL</t>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>KEEP</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -1095,9 +1129,11 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Canonical "how to start a voice AI agency" (Academy entry).</t>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>Distinct 60-day-plan format (only 2 queries). Pair with the reframed how-to-start page; consider merging later.</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1174,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -1181,7 +1219,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1224,7 +1264,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1267,7 +1309,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1310,7 +1354,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1353,7 +1399,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1396,7 +1444,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1443,7 +1493,17 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Chatbot; 301 to voice canvas.</t>
         </is>
@@ -1486,7 +1546,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1529,7 +1591,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1572,7 +1636,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1615,7 +1681,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -1658,7 +1726,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -1701,7 +1771,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -1744,7 +1816,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1787,7 +1861,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1830,7 +1906,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1873,7 +1951,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1920,7 +2000,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>Fold into the canonical pricing guide; 301.</t>
         </is>
@@ -1963,7 +2053,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>Canonical agency-economics post.</t>
         </is>
@@ -2006,7 +2098,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2041,7 +2135,9 @@
           <t>C · interlink/prune (no traffic)</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2084,7 +2180,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2127,7 +2225,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2170,7 +2270,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -2217,7 +2319,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>Fold into canonical roundup; 301.</t>
         </is>
@@ -2264,7 +2376,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>Chatbot-framed; 301 to voice roundup.</t>
         </is>
@@ -2311,7 +2433,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>Fold into canonical roundup; 301.</t>
         </is>
@@ -2354,7 +2486,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>Distinct build-vs-buy angle; keep as canonical build-vs-buy.</t>
         </is>
@@ -2397,7 +2531,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2440,7 +2576,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K44" s="4" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2483,7 +2621,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K45" s="4" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2526,7 +2666,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K46" s="4" t="inlineStr">
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="4" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr">
         <is>
           <t>Distinct "cheapest" price intent; keep, link to hub + pricing guide.</t>
         </is>
@@ -2569,7 +2711,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2612,7 +2756,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K48" s="4" t="inlineStr">
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2655,7 +2801,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K49" s="4" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2698,7 +2846,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K50" s="4" t="inlineStr">
+      <c r="K50" s="5" t="inlineStr"/>
+      <c r="L50" s="4" t="inlineStr"/>
+      <c r="M50" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2741,7 +2891,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="K51" s="5" t="inlineStr"/>
+      <c r="L51" s="4" t="inlineStr"/>
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2784,7 +2936,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K52" s="4" t="inlineStr">
+      <c r="K52" s="5" t="inlineStr"/>
+      <c r="L52" s="4" t="inlineStr"/>
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2831,7 +2985,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K53" s="4" t="inlineStr">
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
         <is>
           <t>Fold into canonical roundup; 301.</t>
         </is>
@@ -2874,7 +3038,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K54" s="4" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2917,7 +3083,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K55" s="4" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2960,7 +3128,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K56" s="4" t="inlineStr">
+      <c r="K56" s="5" t="inlineStr"/>
+      <c r="L56" s="4" t="inlineStr"/>
+      <c r="M56" s="4" t="inlineStr">
         <is>
           <t>Distinct how-to; keep as GHL spoke.</t>
         </is>
@@ -3007,7 +3177,17 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K57" s="4" t="inlineStr">
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM - review shared</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
         <is>
           <t>Same intent; merge + 301.</t>
         </is>
@@ -3050,7 +3230,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K58" s="4" t="inlineStr">
+      <c r="K58" s="5" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr">
         <is>
           <t>Distinct angle; keep as GHL spoke.</t>
         </is>
@@ -3097,7 +3279,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr">
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
         <is>
           <t>Fold into the new GHL landing page; 301.</t>
         </is>
@@ -3144,7 +3336,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K60" s="4" t="inlineStr">
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM - review shared</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
         <is>
           <t>Same intent; merge + 301.</t>
         </is>
@@ -3187,7 +3389,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K61" s="4" t="inlineStr">
+      <c r="K61" s="5" t="inlineStr"/>
+      <c r="L61" s="4" t="inlineStr"/>
+      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -3230,7 +3434,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K62" s="4" t="inlineStr">
+      <c r="K62" s="5" t="inlineStr"/>
+      <c r="L62" s="4" t="inlineStr"/>
+      <c r="M62" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3269,7 +3475,17 @@
           <t>C · interlink/prune (no traffic)</t>
         </is>
       </c>
-      <c r="K63" s="4" t="inlineStr">
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>SOURCE HAS NO QUERIES - safe to redirect</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>Chatbot definitional; 301 to voice.</t>
         </is>
@@ -3312,7 +3528,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K64" s="4" t="inlineStr">
+      <c r="K64" s="5" t="inlineStr"/>
+      <c r="L64" s="4" t="inlineStr"/>
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>Distinct cost-to-start intent; keep.</t>
         </is>
@@ -3359,7 +3577,17 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr">
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
         <is>
           <t>Same intent; merge + 301.</t>
         </is>
@@ -3402,7 +3630,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K66" s="4" t="inlineStr">
+      <c r="K66" s="5" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr"/>
+      <c r="M66" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3445,7 +3675,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K67" s="4" t="inlineStr">
+      <c r="K67" s="5" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr"/>
+      <c r="M67" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3492,7 +3724,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K68" s="4" t="inlineStr">
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="inlineStr">
         <is>
           <t>Chatbot; 301 to voice features checklist.</t>
         </is>
@@ -3535,7 +3777,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K69" s="4" t="inlineStr">
+      <c r="K69" s="5" t="inlineStr"/>
+      <c r="L69" s="4" t="inlineStr"/>
+      <c r="M69" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3578,7 +3822,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K70" s="4" t="inlineStr">
+      <c r="K70" s="5" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3621,7 +3867,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K71" s="4" t="inlineStr">
+      <c r="K71" s="5" t="inlineStr"/>
+      <c r="L71" s="4" t="inlineStr"/>
+      <c r="M71" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3641,16 +3889,12 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
-        <is>
-          <t>REDIRECT</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>/blogs/60-day-ai-voice-agency-launch-plan</t>
-        </is>
-      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>REFRAME</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="5" t="n">
         <v>25911</v>
       </c>
@@ -3668,9 +3912,19 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t>Chatbot-framed start; 301 to voice launch plan.</t>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>GSC: 96 queries — too much traffic to redirect. Rewrite to voice framing ("how to start a voice AI agency") and keep the URL as a primary start guide.</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3965,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr">
+      <c r="K73" s="5" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr"/>
+      <c r="M73" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3754,7 +4010,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
+      <c r="K74" s="5" t="inlineStr"/>
+      <c r="L74" s="4" t="inlineStr"/>
+      <c r="M74" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3797,7 +4055,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K75" s="4" t="inlineStr">
+      <c r="K75" s="5" t="inlineStr"/>
+      <c r="L75" s="4" t="inlineStr"/>
+      <c r="M75" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -3840,7 +4100,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K76" s="4" t="inlineStr">
+      <c r="K76" s="5" t="inlineStr"/>
+      <c r="L76" s="4" t="inlineStr"/>
+      <c r="M76" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -3883,7 +4145,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr">
+      <c r="K77" s="5" t="inlineStr"/>
+      <c r="L77" s="4" t="inlineStr"/>
+      <c r="M77" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3926,7 +4190,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K78" s="4" t="inlineStr">
+      <c r="K78" s="5" t="inlineStr"/>
+      <c r="L78" s="4" t="inlineStr"/>
+      <c r="M78" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -3969,7 +4235,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr">
+      <c r="K79" s="5" t="inlineStr"/>
+      <c r="L79" s="4" t="inlineStr"/>
+      <c r="M79" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -4012,7 +4280,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr"/>
+      <c r="L80" s="4" t="inlineStr"/>
+      <c r="M80" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4055,7 +4325,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K81" s="4" t="inlineStr">
+      <c r="K81" s="5" t="inlineStr"/>
+      <c r="L81" s="4" t="inlineStr"/>
+      <c r="M81" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4102,7 +4374,17 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K82" s="4" t="inlineStr">
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M82" s="4" t="inlineStr">
         <is>
           <t>Same intent; merge as a section + 301.</t>
         </is>
@@ -4145,7 +4427,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr">
+      <c r="K83" s="5" t="inlineStr"/>
+      <c r="L83" s="4" t="inlineStr"/>
+      <c r="M83" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -4188,7 +4472,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K84" s="4" t="inlineStr">
+      <c r="K84" s="5" t="inlineStr"/>
+      <c r="L84" s="4" t="inlineStr"/>
+      <c r="M84" s="4" t="inlineStr">
         <is>
           <t>SERP-validated (keep): ranks #2 for "my ai front desk alternative" — distinct intent from the vs.</t>
         </is>
@@ -4231,7 +4517,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K85" s="4" t="inlineStr">
+      <c r="K85" s="5" t="inlineStr"/>
+      <c r="L85" s="4" t="inlineStr"/>
+      <c r="M85" s="4" t="inlineStr">
         <is>
           <t>SERP-validated (keep): distinct white-label angle; differentiate from alternative-2026 (general) and the vs (head-to-head).</t>
         </is>
@@ -4274,7 +4562,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K86" s="4" t="inlineStr">
+      <c r="K86" s="5" t="inlineStr"/>
+      <c r="L86" s="4" t="inlineStr"/>
+      <c r="M86" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -4317,7 +4607,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K87" s="4" t="inlineStr">
+      <c r="K87" s="5" t="inlineStr"/>
+      <c r="L87" s="4" t="inlineStr"/>
+      <c r="M87" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -4360,7 +4652,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K88" s="4" t="inlineStr">
+      <c r="K88" s="5" t="inlineStr"/>
+      <c r="L88" s="4" t="inlineStr"/>
+      <c r="M88" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4403,7 +4697,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K89" s="4" t="inlineStr">
+      <c r="K89" s="5" t="inlineStr"/>
+      <c r="L89" s="4" t="inlineStr"/>
+      <c r="M89" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4446,7 +4742,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K90" s="4" t="inlineStr">
+      <c r="K90" s="5" t="inlineStr"/>
+      <c r="L90" s="4" t="inlineStr"/>
+      <c r="M90" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4489,7 +4787,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K91" s="4" t="inlineStr">
+      <c r="K91" s="5" t="inlineStr"/>
+      <c r="L91" s="4" t="inlineStr"/>
+      <c r="M91" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -4532,7 +4832,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K92" s="4" t="inlineStr">
+      <c r="K92" s="5" t="inlineStr"/>
+      <c r="L92" s="4" t="inlineStr"/>
+      <c r="M92" s="4" t="inlineStr">
         <is>
           <t>SERP-validated (keep): owns the converting "retell ai white label" niche (3.35% CTR); distinct intent from the head-to-head vs.</t>
         </is>
@@ -4575,7 +4877,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K93" s="4" t="inlineStr">
+      <c r="K93" s="5" t="inlineStr"/>
+      <c r="L93" s="4" t="inlineStr"/>
+      <c r="M93" s="4" t="inlineStr">
         <is>
           <t>SERP-validated (keep): "smith ai alternative" is roundup intent, distinct from the head-to-head vs.</t>
         </is>
@@ -4618,7 +4922,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K94" s="4" t="inlineStr">
+      <c r="K94" s="5" t="inlineStr"/>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4661,7 +4967,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K95" s="4" t="inlineStr">
+      <c r="K95" s="5" t="inlineStr"/>
+      <c r="L95" s="4" t="inlineStr"/>
+      <c r="M95" s="4" t="inlineStr">
         <is>
           <t>SERP-validated (keep): distinct agency-angle content; co-ranks only on the brand term. Differentiate from the vs.</t>
         </is>
@@ -4704,7 +5012,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K96" s="4" t="inlineStr">
+      <c r="K96" s="5" t="inlineStr"/>
+      <c r="L96" s="4" t="inlineStr"/>
+      <c r="M96" s="4" t="inlineStr">
         <is>
           <t>Canonical head-to-head. synthflow-alternative-for-agencies has distinct content and is KEPT (SERP-validated).</t>
         </is>
@@ -4747,7 +5057,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K97" s="4" t="inlineStr">
+      <c r="K97" s="5" t="inlineStr"/>
+      <c r="L97" s="4" t="inlineStr"/>
+      <c r="M97" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4790,7 +5102,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K98" s="4" t="inlineStr">
+      <c r="K98" s="5" t="inlineStr"/>
+      <c r="L98" s="4" t="inlineStr"/>
+      <c r="M98" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4810,7 +5124,7 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D99" s="14" t="inlineStr">
+      <c r="D99" s="15" t="inlineStr">
         <is>
           <t>REVAMP</t>
         </is>
@@ -4833,7 +5147,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K99" s="4" t="inlineStr">
+      <c r="K99" s="5" t="inlineStr"/>
+      <c r="L99" s="4" t="inlineStr"/>
+      <c r="M99" s="4" t="inlineStr">
         <is>
           <t>Canonical "best white-label voice AI" roundup. Rewrite as honest named comparison + current data.</t>
         </is>
@@ -4876,7 +5192,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K100" s="4" t="inlineStr">
+      <c r="K100" s="5" t="inlineStr"/>
+      <c r="L100" s="4" t="inlineStr"/>
+      <c r="M100" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4919,7 +5237,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K101" s="4" t="inlineStr">
+      <c r="K101" s="5" t="inlineStr"/>
+      <c r="L101" s="4" t="inlineStr"/>
+      <c r="M101" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4962,7 +5282,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K102" s="4" t="inlineStr">
+      <c r="K102" s="5" t="inlineStr"/>
+      <c r="L102" s="4" t="inlineStr"/>
+      <c r="M102" s="4" t="inlineStr">
         <is>
           <t>Canonical "GHL native vs Trillet" comparison.</t>
         </is>
@@ -5005,7 +5327,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K103" s="4" t="inlineStr">
+      <c r="K103" s="5" t="inlineStr"/>
+      <c r="L103" s="4" t="inlineStr"/>
+      <c r="M103" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5048,7 +5372,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K104" s="4" t="inlineStr">
+      <c r="K104" s="5" t="inlineStr"/>
+      <c r="L104" s="4" t="inlineStr"/>
+      <c r="M104" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5091,7 +5417,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K105" s="4" t="inlineStr">
+      <c r="K105" s="5" t="inlineStr"/>
+      <c r="L105" s="4" t="inlineStr"/>
+      <c r="M105" s="4" t="inlineStr">
         <is>
           <t>Canonical head-to-head. The two MAFD alternative pages serve different intent and are KEPT (SERP-validated), not merged here.</t>
         </is>
@@ -5134,7 +5462,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K106" s="4" t="inlineStr">
+      <c r="K106" s="5" t="inlineStr"/>
+      <c r="L106" s="4" t="inlineStr"/>
+      <c r="M106" s="4" t="inlineStr">
         <is>
           <t>Canonical head-to-head. The Retell/Vapi white-label "alternative" pages own distinct intent and are KEPT (SERP-validated).</t>
         </is>
@@ -5177,7 +5507,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K107" s="4" t="inlineStr">
+      <c r="K107" s="5" t="inlineStr"/>
+      <c r="L107" s="4" t="inlineStr"/>
+      <c r="M107" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5220,7 +5552,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K108" s="4" t="inlineStr">
+      <c r="K108" s="5" t="inlineStr"/>
+      <c r="L108" s="4" t="inlineStr"/>
+      <c r="M108" s="4" t="inlineStr">
         <is>
           <t>Canonical head-to-head. smith-ai-alternative-2026 owns roundup intent and is KEPT (SERP-validated).</t>
         </is>
@@ -5263,7 +5597,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K109" s="4" t="inlineStr">
+      <c r="K109" s="5" t="inlineStr"/>
+      <c r="L109" s="4" t="inlineStr"/>
+      <c r="M109" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5306,7 +5642,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K110" s="4" t="inlineStr">
+      <c r="K110" s="5" t="inlineStr"/>
+      <c r="L110" s="4" t="inlineStr"/>
+      <c r="M110" s="4" t="inlineStr">
         <is>
           <t>SERP-validated (keep): ranks p1 (#3) for "vapi alternative for agencies" — roundup intent, distinct from the vs.</t>
         </is>
@@ -5349,7 +5687,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K111" s="4" t="inlineStr">
+      <c r="K111" s="5" t="inlineStr"/>
+      <c r="L111" s="4" t="inlineStr"/>
+      <c r="M111" s="4" t="inlineStr">
         <is>
           <t>Distinct compliance angle (the wedge); keep.</t>
         </is>
@@ -5392,7 +5732,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K112" s="4" t="inlineStr">
+      <c r="K112" s="5" t="inlineStr"/>
+      <c r="L112" s="4" t="inlineStr"/>
+      <c r="M112" s="4" t="inlineStr">
         <is>
           <t>Distinct: Vapi own WL options; keep.</t>
         </is>
@@ -5435,7 +5777,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K113" s="4" t="inlineStr">
+      <c r="K113" s="5" t="inlineStr"/>
+      <c r="L113" s="4" t="inlineStr"/>
+      <c r="M113" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5478,7 +5822,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K114" s="4" t="inlineStr">
+      <c r="K114" s="5" t="inlineStr"/>
+      <c r="L114" s="4" t="inlineStr"/>
+      <c r="M114" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -5521,7 +5867,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K115" s="4" t="inlineStr">
+      <c r="K115" s="5" t="inlineStr"/>
+      <c r="L115" s="4" t="inlineStr"/>
+      <c r="M115" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -5564,7 +5912,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K116" s="4" t="inlineStr">
+      <c r="K116" s="5" t="inlineStr"/>
+      <c r="L116" s="4" t="inlineStr"/>
+      <c r="M116" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -5607,7 +5957,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K117" s="4" t="inlineStr">
+      <c r="K117" s="5" t="inlineStr"/>
+      <c r="L117" s="4" t="inlineStr"/>
+      <c r="M117" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -5650,7 +6002,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K118" s="4" t="inlineStr">
+      <c r="K118" s="5" t="inlineStr"/>
+      <c r="L118" s="4" t="inlineStr"/>
+      <c r="M118" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -5693,7 +6047,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K119" s="4" t="inlineStr">
+      <c r="K119" s="5" t="inlineStr"/>
+      <c r="L119" s="4" t="inlineStr"/>
+      <c r="M119" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -5736,7 +6092,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K120" s="4" t="inlineStr">
+      <c r="K120" s="5" t="inlineStr"/>
+      <c r="L120" s="4" t="inlineStr"/>
+      <c r="M120" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5756,7 +6114,7 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D121" s="15" t="inlineStr">
+      <c r="D121" s="14" t="inlineStr">
         <is>
           <t>REFRAME</t>
         </is>
@@ -5771,7 +6129,9 @@
           <t>C · interlink/prune (no traffic)</t>
         </is>
       </c>
-      <c r="K121" s="4" t="inlineStr">
+      <c r="K121" s="5" t="inlineStr"/>
+      <c r="L121" s="4" t="inlineStr"/>
+      <c r="M121" s="4" t="inlineStr">
         <is>
           <t>KEEP but sharpen "sell voice, not chat"; the chatbot-&gt;voice converter.</t>
         </is>
@@ -5814,7 +6174,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K122" s="4" t="inlineStr">
+      <c r="K122" s="5" t="inlineStr"/>
+      <c r="L122" s="4" t="inlineStr"/>
+      <c r="M122" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -5857,7 +6219,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K123" s="4" t="inlineStr">
+      <c r="K123" s="5" t="inlineStr"/>
+      <c r="L123" s="4" t="inlineStr"/>
+      <c r="M123" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -5900,7 +6264,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K124" s="4" t="inlineStr">
+      <c r="K124" s="5" t="inlineStr"/>
+      <c r="L124" s="4" t="inlineStr"/>
+      <c r="M124" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -5943,7 +6309,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K125" s="4" t="inlineStr">
+      <c r="K125" s="5" t="inlineStr"/>
+      <c r="L125" s="4" t="inlineStr"/>
+      <c r="M125" s="4" t="inlineStr">
         <is>
           <t>Distinct ROI tool; keep.</t>
         </is>
@@ -5982,7 +6350,17 @@
           <t>C · interlink/prune (no traffic)</t>
         </is>
       </c>
-      <c r="K126" s="4" t="inlineStr">
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>SOURCE HAS NO QUERIES - safe to redirect</t>
+        </is>
+      </c>
+      <c r="M126" s="4" t="inlineStr">
         <is>
           <t>Merge + 301.</t>
         </is>
@@ -6025,7 +6403,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K127" s="4" t="inlineStr">
+      <c r="K127" s="5" t="inlineStr"/>
+      <c r="L127" s="4" t="inlineStr"/>
+      <c r="M127" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -6060,7 +6440,9 @@
           <t>C · interlink/prune (no traffic)</t>
         </is>
       </c>
-      <c r="K128" s="4" t="inlineStr">
+      <c r="K128" s="5" t="inlineStr"/>
+      <c r="L128" s="4" t="inlineStr"/>
+      <c r="M128" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -6103,7 +6485,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K129" s="4" t="inlineStr">
+      <c r="K129" s="5" t="inlineStr"/>
+      <c r="L129" s="4" t="inlineStr"/>
+      <c r="M129" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6146,7 +6530,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K130" s="4" t="inlineStr">
+      <c r="K130" s="5" t="inlineStr"/>
+      <c r="L130" s="4" t="inlineStr"/>
+      <c r="M130" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6189,7 +6575,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K131" s="4" t="inlineStr">
+      <c r="K131" s="5" t="inlineStr"/>
+      <c r="L131" s="4" t="inlineStr"/>
+      <c r="M131" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6232,7 +6620,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K132" s="4" t="inlineStr">
+      <c r="K132" s="5" t="inlineStr"/>
+      <c r="L132" s="4" t="inlineStr"/>
+      <c r="M132" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6275,7 +6665,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K133" s="4" t="inlineStr">
+      <c r="K133" s="5" t="inlineStr"/>
+      <c r="L133" s="4" t="inlineStr"/>
+      <c r="M133" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6318,7 +6710,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K134" s="4" t="inlineStr">
+      <c r="K134" s="5" t="inlineStr"/>
+      <c r="L134" s="4" t="inlineStr"/>
+      <c r="M134" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6361,7 +6755,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K135" s="4" t="inlineStr">
+      <c r="K135" s="5" t="inlineStr"/>
+      <c r="L135" s="4" t="inlineStr"/>
+      <c r="M135" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6404,7 +6800,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K136" s="4" t="inlineStr">
+      <c r="K136" s="5" t="inlineStr"/>
+      <c r="L136" s="4" t="inlineStr"/>
+      <c r="M136" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6447,7 +6845,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K137" s="4" t="inlineStr">
+      <c r="K137" s="5" t="inlineStr"/>
+      <c r="L137" s="4" t="inlineStr"/>
+      <c r="M137" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6490,7 +6890,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K138" s="4" t="inlineStr">
+      <c r="K138" s="5" t="inlineStr"/>
+      <c r="L138" s="4" t="inlineStr"/>
+      <c r="M138" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6533,7 +6935,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K139" s="4" t="inlineStr">
+      <c r="K139" s="5" t="inlineStr"/>
+      <c r="L139" s="4" t="inlineStr"/>
+      <c r="M139" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -6576,7 +6980,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K140" s="4" t="inlineStr">
+      <c r="K140" s="5" t="inlineStr"/>
+      <c r="L140" s="4" t="inlineStr"/>
+      <c r="M140" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -6619,7 +7025,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K141" s="4" t="inlineStr">
+      <c r="K141" s="5" t="inlineStr"/>
+      <c r="L141" s="4" t="inlineStr"/>
+      <c r="M141" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -6662,7 +7070,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K142" s="4" t="inlineStr">
+      <c r="K142" s="5" t="inlineStr"/>
+      <c r="L142" s="4" t="inlineStr"/>
+      <c r="M142" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -6705,7 +7115,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K143" s="4" t="inlineStr">
+      <c r="K143" s="5" t="inlineStr"/>
+      <c r="L143" s="4" t="inlineStr"/>
+      <c r="M143" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -6748,7 +7160,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K144" s="4" t="inlineStr">
+      <c r="K144" s="5" t="inlineStr"/>
+      <c r="L144" s="4" t="inlineStr"/>
+      <c r="M144" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -6775,7 +7189,7 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>/blogs/voice-first-vs-chat-first-platforms</t>
+          <t>/blogs/voice-ai-vs-text-chatbot-comparison</t>
         </is>
       </c>
       <c r="F145" s="5" t="n">
@@ -6795,7 +7209,17 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K145" s="4" t="inlineStr">
+      <c r="K145" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M145" s="4" t="inlineStr">
         <is>
           <t>Merge + 301.</t>
         </is>
@@ -6815,16 +7239,12 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D146" s="13" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>/blogs/voice-first-vs-chat-first-platforms</t>
-        </is>
-      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>CANONICAL</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr"/>
       <c r="F146" s="5" t="n">
         <v>8335</v>
       </c>
@@ -6842,9 +7262,19 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K146" s="4" t="inlineStr">
-        <is>
-          <t>Merge + 301.</t>
+      <c r="K146" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M146" s="4" t="inlineStr">
+        <is>
+          <t>GSC-validated survivor: 75 queries vs 21 on the alternative. Canonical voice-vs-text post.</t>
         </is>
       </c>
     </row>
@@ -6862,7 +7292,7 @@
           <t>5 · Pricing &amp; economics</t>
         </is>
       </c>
-      <c r="D147" s="14" t="inlineStr">
+      <c r="D147" s="15" t="inlineStr">
         <is>
           <t>REVAMP</t>
         </is>
@@ -6885,7 +7315,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K147" s="4" t="inlineStr">
+      <c r="K147" s="5" t="inlineStr"/>
+      <c r="L147" s="4" t="inlineStr"/>
+      <c r="M147" s="4" t="inlineStr">
         <is>
           <t>Canonical WL-pricing GUIDE. 46k impressions @0.06% CTR — rewrite title/meta/snippet, add table + CTA to /whitelabel/pricing.</t>
         </is>
@@ -6928,7 +7360,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K148" s="4" t="inlineStr">
+      <c r="K148" s="5" t="inlineStr"/>
+      <c r="L148" s="4" t="inlineStr"/>
+      <c r="M148" s="4" t="inlineStr">
         <is>
           <t>Canonical wrapper-vs-native (the "we own the stack" differentiator).</t>
         </is>
@@ -6948,12 +7382,16 @@
           <t>4 · Compare</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>CANONICAL</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="inlineStr"/>
+      <c r="D149" s="13" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>/blogs/voice-ai-vs-text-chatbot-comparison</t>
+        </is>
+      </c>
       <c r="F149" s="5" t="n">
         <v>2149</v>
       </c>
@@ -6971,9 +7409,11 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K149" s="4" t="inlineStr">
-        <is>
-          <t>Canonical voice-vs-text positioning post.</t>
+      <c r="K149" s="5" t="inlineStr"/>
+      <c r="L149" s="4" t="inlineStr"/>
+      <c r="M149" s="4" t="inlineStr">
+        <is>
+          <t>Fewer queries (21 vs 75); merge into the stronger page + 301.</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7454,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K150" s="4" t="inlineStr">
+      <c r="K150" s="5" t="inlineStr"/>
+      <c r="L150" s="4" t="inlineStr"/>
+      <c r="M150" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -7057,7 +7499,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K151" s="4" t="inlineStr">
+      <c r="K151" s="5" t="inlineStr"/>
+      <c r="L151" s="4" t="inlineStr"/>
+      <c r="M151" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -7100,7 +7544,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K152" s="4" t="inlineStr">
+      <c r="K152" s="5" t="inlineStr"/>
+      <c r="L152" s="4" t="inlineStr"/>
+      <c r="M152" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -7143,7 +7589,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K153" s="4" t="inlineStr">
+      <c r="K153" s="5" t="inlineStr"/>
+      <c r="L153" s="4" t="inlineStr"/>
+      <c r="M153" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -7186,7 +7634,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K154" s="4" t="inlineStr">
+      <c r="K154" s="5" t="inlineStr"/>
+      <c r="L154" s="4" t="inlineStr"/>
+      <c r="M154" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -7233,7 +7683,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K155" s="4" t="inlineStr">
+      <c r="K155" s="5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M155" s="4" t="inlineStr">
         <is>
           <t>Chatbot definitional; 301 to voice.</t>
         </is>
@@ -7276,7 +7736,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K156" s="4" t="inlineStr">
+      <c r="K156" s="5" t="inlineStr"/>
+      <c r="L156" s="4" t="inlineStr"/>
+      <c r="M156" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -7319,7 +7781,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K157" s="4" t="inlineStr">
+      <c r="K157" s="5" t="inlineStr"/>
+      <c r="L157" s="4" t="inlineStr"/>
+      <c r="M157" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -7362,7 +7826,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K158" s="4" t="inlineStr">
+      <c r="K158" s="5" t="inlineStr"/>
+      <c r="L158" s="4" t="inlineStr"/>
+      <c r="M158" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -7405,7 +7871,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K159" s="4" t="inlineStr">
+      <c r="K159" s="5" t="inlineStr"/>
+      <c r="L159" s="4" t="inlineStr"/>
+      <c r="M159" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -7452,7 +7920,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K160" s="4" t="inlineStr">
+      <c r="K160" s="5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M160" s="4" t="inlineStr">
         <is>
           <t>Chatbot-framed; 301 to voice pricing guide.</t>
         </is>
@@ -7499,7 +7977,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K161" s="4" t="inlineStr">
+      <c r="K161" s="5" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="L161" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M161" s="4" t="inlineStr">
         <is>
           <t>Merge tool into voice ROI model; 301.</t>
         </is>
@@ -7542,7 +8030,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K162" s="4" t="inlineStr">
+      <c r="K162" s="5" t="inlineStr"/>
+      <c r="L162" s="4" t="inlineStr"/>
+      <c r="M162" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -7585,7 +8075,9 @@
           <t>C · interlink/prune</t>
         </is>
       </c>
-      <c r="K163" s="4" t="inlineStr">
+      <c r="K163" s="5" t="inlineStr"/>
+      <c r="L163" s="4" t="inlineStr"/>
+      <c r="M163" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -7628,7 +8120,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K164" s="4" t="inlineStr">
+      <c r="K164" s="5" t="inlineStr"/>
+      <c r="L164" s="4" t="inlineStr"/>
+      <c r="M164" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -7671,7 +8165,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K165" s="4" t="inlineStr">
+      <c r="K165" s="5" t="inlineStr"/>
+      <c r="L165" s="4" t="inlineStr"/>
+      <c r="M165" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -7714,7 +8210,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K166" s="4" t="inlineStr">
+      <c r="K166" s="5" t="inlineStr"/>
+      <c r="L166" s="4" t="inlineStr"/>
+      <c r="M166" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -7757,7 +8255,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K167" s="4" t="inlineStr">
+      <c r="K167" s="5" t="inlineStr"/>
+      <c r="L167" s="4" t="inlineStr"/>
+      <c r="M167" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -7800,7 +8300,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K168" s="4" t="inlineStr">
+      <c r="K168" s="5" t="inlineStr"/>
+      <c r="L168" s="4" t="inlineStr"/>
+      <c r="M168" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -7843,7 +8345,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K169" s="4" t="inlineStr">
+      <c r="K169" s="5" t="inlineStr"/>
+      <c r="L169" s="4" t="inlineStr"/>
+      <c r="M169" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -7890,7 +8394,17 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K170" s="4" t="inlineStr">
+      <c r="K170" s="5" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM - review shared</t>
+        </is>
+      </c>
+      <c r="M170" s="4" t="inlineStr">
         <is>
           <t>Near-duplicate; merge + 301.</t>
         </is>
@@ -7933,7 +8447,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K171" s="4" t="inlineStr">
+      <c r="K171" s="5" t="inlineStr"/>
+      <c r="L171" s="4" t="inlineStr"/>
+      <c r="M171" s="4" t="inlineStr">
         <is>
           <t>Canonical profit-margins post.</t>
         </is>
@@ -7976,7 +8492,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K172" s="4" t="inlineStr">
+      <c r="K172" s="5" t="inlineStr"/>
+      <c r="L172" s="4" t="inlineStr"/>
+      <c r="M172" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -8019,7 +8537,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K173" s="4" t="inlineStr">
+      <c r="K173" s="5" t="inlineStr"/>
+      <c r="L173" s="4" t="inlineStr"/>
+      <c r="M173" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8062,7 +8582,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K174" s="4" t="inlineStr">
+      <c r="K174" s="5" t="inlineStr"/>
+      <c r="L174" s="4" t="inlineStr"/>
+      <c r="M174" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8105,7 +8627,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K175" s="4" t="inlineStr">
+      <c r="K175" s="5" t="inlineStr"/>
+      <c r="L175" s="4" t="inlineStr"/>
+      <c r="M175" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8148,7 +8672,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K176" s="4" t="inlineStr">
+      <c r="K176" s="5" t="inlineStr"/>
+      <c r="L176" s="4" t="inlineStr"/>
+      <c r="M176" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8191,7 +8717,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K177" s="4" t="inlineStr">
+      <c r="K177" s="5" t="inlineStr"/>
+      <c r="L177" s="4" t="inlineStr"/>
+      <c r="M177" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8234,7 +8762,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K178" s="4" t="inlineStr">
+      <c r="K178" s="5" t="inlineStr"/>
+      <c r="L178" s="4" t="inlineStr"/>
+      <c r="M178" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8281,7 +8811,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K179" s="4" t="inlineStr">
+      <c r="K179" s="5" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="L179" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M179" s="4" t="inlineStr">
         <is>
           <t>Off-topic (chatgpt); 301 to hub.</t>
         </is>
@@ -8324,7 +8864,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K180" s="4" t="inlineStr">
+      <c r="K180" s="5" t="inlineStr"/>
+      <c r="L180" s="4" t="inlineStr"/>
+      <c r="M180" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8367,7 +8909,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K181" s="4" t="inlineStr">
+      <c r="K181" s="5" t="inlineStr"/>
+      <c r="L181" s="4" t="inlineStr"/>
+      <c r="M181" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8410,7 +8954,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K182" s="4" t="inlineStr">
+      <c r="K182" s="5" t="inlineStr"/>
+      <c r="L182" s="4" t="inlineStr"/>
+      <c r="M182" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8453,7 +8999,9 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K183" s="4" t="inlineStr">
+      <c r="K183" s="5" t="inlineStr"/>
+      <c r="L183" s="4" t="inlineStr"/>
+      <c r="M183" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8500,9 +9048,19 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K184" s="4" t="inlineStr">
-        <is>
-          <t>Merge + 301.</t>
+      <c r="K184" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L184" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M184" s="4" t="inlineStr">
+        <is>
+          <t>Merge + 301. SURVIVOR REVIEW: this source has 13 queries vs 2 on the target — confirm which URL survives before 301.</t>
         </is>
       </c>
     </row>
@@ -8547,7 +9105,17 @@
           <t>A · deep revamp</t>
         </is>
       </c>
-      <c r="K185" s="4" t="inlineStr">
+      <c r="K185" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L185" s="4" t="inlineStr">
+        <is>
+          <t>LOW - keep both</t>
+        </is>
+      </c>
+      <c r="M185" s="4" t="inlineStr">
         <is>
           <t>Chatbot build-vs-buy; 301 to canonical build-vs-buy.</t>
         </is>
@@ -8590,7 +9158,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K186" s="4" t="inlineStr">
+      <c r="K186" s="5" t="inlineStr"/>
+      <c r="L186" s="4" t="inlineStr"/>
+      <c r="M186" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8633,7 +9203,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K187" s="4" t="inlineStr">
+      <c r="K187" s="5" t="inlineStr"/>
+      <c r="L187" s="4" t="inlineStr"/>
+      <c r="M187" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -8676,7 +9248,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K188" s="4" t="inlineStr">
+      <c r="K188" s="5" t="inlineStr"/>
+      <c r="L188" s="4" t="inlineStr"/>
+      <c r="M188" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -8719,7 +9293,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K189" s="4" t="inlineStr">
+      <c r="K189" s="5" t="inlineStr"/>
+      <c r="L189" s="4" t="inlineStr"/>
+      <c r="M189" s="4" t="inlineStr">
         <is>
           <t>Revamp under the program hub.</t>
         </is>
@@ -8762,7 +9338,9 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K190" s="4" t="inlineStr">
+      <c r="K190" s="5" t="inlineStr"/>
+      <c r="L190" s="4" t="inlineStr"/>
+      <c r="M190" s="4" t="inlineStr">
         <is>
           <t>Revamp; link from voice-ai-agency-referral-program.</t>
         </is>
@@ -8805,14 +9383,16 @@
           <t>B · light revamp</t>
         </is>
       </c>
-      <c r="K191" s="4" t="inlineStr">
+      <c r="K191" s="5" t="inlineStr"/>
+      <c r="L191" s="4" t="inlineStr"/>
+      <c r="M191" s="4" t="inlineStr">
         <is>
           <t>Revamp under the program hub; wire Academy posts to it.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K191"/>
+  <autoFilter ref="A1:M191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8859,7 +9439,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -8879,7 +9459,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6">
@@ -8899,7 +9479,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -8909,7 +9489,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">

--- a/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
+++ b/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Data findings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Redirect map'!$A$1:$M$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Redirect map'!$A$1:$M$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M191"/>
+  <dimension ref="A1:M192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2406,16 +2406,12 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>/blogs/top-10-white-label-voice-ai-platforms-for-agencies-2026</t>
-        </is>
-      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>CANONICAL</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="5" t="n">
         <v>12333</v>
       </c>
@@ -2445,7 +2441,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Fold into canonical roundup; 301.</t>
+          <t>GSC: pos 6.5 for "white label ai receptionist", 17 clicks (top non-brand converter in the cluster). Keep as canonical for the receptionist money term - do NOT merge.</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5147,7 @@
       <c r="L99" s="4" t="inlineStr"/>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>Canonical "best white-label voice AI" roundup. Rewrite as honest named comparison + current data.</t>
+          <t>Canonical "best white-label voice AI PLATFORMS" roundup (platforms intent). GSC: 130-533 impr on head terms but pos 19-25. best-white-label-ai-receptionist is a SEPARATE winner (receptionist intent) and is NOT merged in.</t>
         </is>
       </c>
     </row>
@@ -9391,8 +9387,57 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>/agency</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>2 · Agency Academy</t>
+        </is>
+      </c>
+      <c r="D192" s="12" t="inlineStr">
+        <is>
+          <t>REDIRECT</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>/whitelabel</t>
+        </is>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>10419</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H192" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I192" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J192" s="6" t="inlineStr">
+        <is>
+          <t>A · deep revamp</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="inlineStr"/>
+      <c r="L192" s="4" t="inlineStr"/>
+      <c r="M192" s="4" t="inlineStr">
+        <is>
+          <t>DUPLICATE of /whitelabel (byte-identical, canonical already points to /whitelabel but is being IGNORED). Not in sitemap yet ranks separately/above /whitelabel for head terms (e.g. pos 39 for "white label ai voice agent", 284 impr). 301 /agency to /whitelabel and remove internal links. GSC-confirmed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M191"/>
+  <autoFilter ref="A1:M192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9439,7 +9484,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -9469,7 +9514,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -9479,7 +9524,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -9531,7 +9576,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -9593,7 +9638,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21">

--- a/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
+++ b/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
@@ -49,7 +49,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -106,6 +106,11 @@
         <fgColor rgb="00CFE0FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9F0DC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -133,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -178,6 +183,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -9401,9 +9409,9 @@
           <t>2 · Agency Academy</t>
         </is>
       </c>
-      <c r="D192" s="12" t="inlineStr">
-        <is>
-          <t>REDIRECT</t>
+      <c r="D192" s="16" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
@@ -9432,7 +9440,7 @@
       <c r="L192" s="4" t="inlineStr"/>
       <c r="M192" s="4" t="inlineStr">
         <is>
-          <t>DUPLICATE of /whitelabel (byte-identical, canonical already points to /whitelabel but is being IGNORED). Not in sitemap yet ranks separately/above /whitelabel for head terms (e.g. pos 39 for "white label ai voice agent", 284 impr). 301 /agency to /whitelabel and remove internal links. GSC-confirmed.</t>
+          <t>ALREADY 308-redirected to /whitelabel (permanent; passes signal like a 301) - NO ACTION. Its historical head-term impressions in the 16-mo data will consolidate into /whitelabel as Google reprocesses (same as the apex/www fix). Only verify no internal links still point to /agency.</t>
         </is>
       </c>
     </row>
@@ -9456,19 +9464,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9478,7 +9486,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>CANONICAL</t>
         </is>
@@ -9488,7 +9496,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>REVAMP</t>
         </is>
@@ -9498,7 +9506,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
@@ -9508,7 +9516,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
@@ -9518,17 +9526,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>REDIRECT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>REFRAME</t>
         </is>
@@ -9538,12 +9546,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
@@ -9620,12 +9628,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Revamp tier (GSC-grounded)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
@@ -9700,144 +9708,144 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Finding</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Window</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>16 months (2025-05-07 to 2026-09-06), Web search</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Site total</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>18,848 clicks · 1,908,737 impressions · 0.99% CTR</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>Impressions grew ~46x as programmatic content shipped (13.5k -&gt; 621k per 90 days); clicks only ~1.8x; CTR fell 19.85% -&gt; 0.76%. Relevance/snippet failure at scale, confirmed — this (not host duplication) is now the primary problem.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Apex/www — RESOLVED</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Host duplication has been canonicalised to a single host (no longer a lever). The 16-mo export still shows both hosts historically; tiers here are deduped by path, i.e. the consolidated single-URL view. Re-pull GSC in 4-8 weeks to measure the consolidation lift.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>WL cluster</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>764,907 impressions = 40% of all site impressions, but only 2,036 clicks @ 0.27% CTR (vs 0.99% site).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Revamp prize (#1 lever now)</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>93 WL pages sit in striking distance (pos&lt;=20, impr&gt;=1000, CTR&lt;1.5%) holding ~721,000 impressions — the Tier-A revamp target and, with apex/www done, the single biggest lever. Note: exclude chatbot-query impressions (structurally unconvertible for a voice product) from any CTR-lift forecast.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>Chatbot = wasted impressions</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>'white label chatbot' 1,569 impr pos 18.9 0.13%; 'chatbot white label' 1,354; 'white label ai chatbot' 1,003; 'whitelabel chatbot' 939; all ~0% CTR. Voice-first Trillet can't convert chatbot demand — reframe/redirect confirmed.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>Voice/receptionist converts</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>'white label ai receptionist' 1,549 impr, 37 clk, 2.39% CTR (best non-brand); 'ai receptionist white label' 1.59%; 'retell ai white label' 3.35%. 10-20x better than chatbot terms at similar positions.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Head terms stuck</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>'white label ai voice agent' pos 26.8; 'white label ai platform' pos 30.6; 'white label voice' pos 19.7 — the terms the /whitelabel hub must win are on page 2-3 today.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>Brand WL demand</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>'trillet white label' 46.73% CTR; 'trillet ai white label' 21.70%. Real branded white-label demand exists and converts.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>Worst offenders (page)</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>voice-ai-white-label-pricing-breakdown-2026 42,150 impr @0.06%; best-white-label-ai-chatbot 39,390 @0.19%; voicify-alternative 26,793 impr @0.00% (1 click).</t>
         </is>

--- a/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
+++ b/seo-audit/Trillet-WhiteLabel-Redirect-Map.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Data findings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Redirect map'!$A$1:$M$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Redirect map'!$A$1:$N$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M192"/>
+  <dimension ref="A1:N192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,8 @@
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="58" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="58" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -649,6 +650,11 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Live HTTP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Reason / note</t>
         </is>
       </c>
@@ -692,7 +698,12 @@
       </c>
       <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>Rebuild as the cluster hub (title/H1/subhead, SoftwareApplication+Offer schema, remove meta-kw, links to all spokes).</t>
         </is>
@@ -737,7 +748,12 @@
       </c>
       <c r="K3" s="5" t="inlineStr"/>
       <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>Canonical pricing target. Point all WL-pricing blogs here.</t>
         </is>
@@ -782,7 +798,12 @@
       </c>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Rebuild as partner-program hub (Reseller/OEM/Referral/Agency tiers, benefits, apply CTA).</t>
         </is>
@@ -819,7 +840,12 @@
       </c>
       <c r="K5" s="5" t="inlineStr"/>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>404 (to build)</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>NEW integrations directory hub.</t>
         </is>
@@ -856,7 +882,12 @@
       </c>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>404 (to build)</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>NEW canonical GoHighLevel landing page (consolidates GHL posts as spokes).</t>
         </is>
@@ -893,7 +924,12 @@
       </c>
       <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>404 (to build)</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>NEW AI Voice Agency Academy hub — organises the ~45 business posts into a learning path.</t>
         </is>
@@ -930,7 +966,12 @@
       </c>
       <c r="K8" s="5" t="inlineStr"/>
       <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>404 (to build)</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>NEW white-label-by-industry index — links the ~25 vertical posts + their /receptionist/industries counterparts.</t>
         </is>
@@ -967,7 +1008,12 @@
       </c>
       <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>404 (to build)</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>NEW compare &amp; alternatives index — links all vs/alternative pages, one per competitor.</t>
         </is>
@@ -1004,7 +1050,12 @@
       </c>
       <c r="K10" s="5" t="inlineStr"/>
       <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>404 (to build)</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>NEW /reviews social-proof hub (Review schema).</t>
         </is>
@@ -1049,7 +1100,12 @@
       </c>
       <c r="K11" s="5" t="inlineStr"/>
       <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1094,7 +1150,12 @@
       </c>
       <c r="K12" s="5" t="inlineStr"/>
       <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1139,7 +1200,12 @@
       </c>
       <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>Distinct 60-day-plan format (only 2 queries). Pair with the reframed how-to-start page; consider merging later.</t>
         </is>
@@ -1184,7 +1250,12 @@
       </c>
       <c r="K14" s="5" t="inlineStr"/>
       <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -1229,7 +1300,12 @@
       </c>
       <c r="K15" s="5" t="inlineStr"/>
       <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1274,7 +1350,12 @@
       </c>
       <c r="K16" s="5" t="inlineStr"/>
       <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1319,7 +1400,12 @@
       </c>
       <c r="K17" s="5" t="inlineStr"/>
       <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1364,7 +1450,12 @@
       </c>
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1409,7 +1500,12 @@
       </c>
       <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1454,7 +1550,12 @@
       </c>
       <c r="K20" s="5" t="inlineStr"/>
       <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1511,7 +1612,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>Chatbot; 301 to voice canvas.</t>
         </is>
@@ -1556,7 +1662,12 @@
       </c>
       <c r="K22" s="5" t="inlineStr"/>
       <c r="L22" s="4" t="inlineStr"/>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1601,7 +1712,12 @@
       </c>
       <c r="K23" s="5" t="inlineStr"/>
       <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1646,7 +1762,12 @@
       </c>
       <c r="K24" s="5" t="inlineStr"/>
       <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1691,7 +1812,12 @@
       </c>
       <c r="K25" s="5" t="inlineStr"/>
       <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -1736,7 +1862,12 @@
       </c>
       <c r="K26" s="5" t="inlineStr"/>
       <c r="L26" s="4" t="inlineStr"/>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -1781,7 +1912,12 @@
       </c>
       <c r="K27" s="5" t="inlineStr"/>
       <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -1826,7 +1962,12 @@
       </c>
       <c r="K28" s="5" t="inlineStr"/>
       <c r="L28" s="4" t="inlineStr"/>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -1871,7 +2012,12 @@
       </c>
       <c r="K29" s="5" t="inlineStr"/>
       <c r="L29" s="4" t="inlineStr"/>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1916,7 +2062,12 @@
       </c>
       <c r="K30" s="5" t="inlineStr"/>
       <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -1961,7 +2112,12 @@
       </c>
       <c r="K31" s="5" t="inlineStr"/>
       <c r="L31" s="4" t="inlineStr"/>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2018,7 +2174,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>Fold into the canonical pricing guide; 301.</t>
         </is>
@@ -2063,7 +2224,12 @@
       </c>
       <c r="K33" s="5" t="inlineStr"/>
       <c r="L33" s="4" t="inlineStr"/>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>Canonical agency-economics post.</t>
         </is>
@@ -2108,7 +2274,12 @@
       </c>
       <c r="K34" s="5" t="inlineStr"/>
       <c r="L34" s="4" t="inlineStr"/>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2145,7 +2316,12 @@
       </c>
       <c r="K35" s="5" t="inlineStr"/>
       <c r="L35" s="4" t="inlineStr"/>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2190,7 +2366,12 @@
       </c>
       <c r="K36" s="5" t="inlineStr"/>
       <c r="L36" s="4" t="inlineStr"/>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2235,7 +2416,12 @@
       </c>
       <c r="K37" s="5" t="inlineStr"/>
       <c r="L37" s="4" t="inlineStr"/>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2280,7 +2466,12 @@
       </c>
       <c r="K38" s="5" t="inlineStr"/>
       <c r="L38" s="4" t="inlineStr"/>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -2337,7 +2528,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>Fold into canonical roundup; 301.</t>
         </is>
@@ -2394,7 +2590,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>Chatbot-framed; 301 to voice roundup.</t>
         </is>
@@ -2447,7 +2648,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>GSC: pos 6.5 for "white label ai receptionist", 17 clicks (top non-brand converter in the cluster). Keep as canonical for the receptionist money term - do NOT merge.</t>
         </is>
@@ -2492,7 +2698,12 @@
       </c>
       <c r="K42" s="5" t="inlineStr"/>
       <c r="L42" s="4" t="inlineStr"/>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>Distinct build-vs-buy angle; keep as canonical build-vs-buy.</t>
         </is>
@@ -2537,7 +2748,12 @@
       </c>
       <c r="K43" s="5" t="inlineStr"/>
       <c r="L43" s="4" t="inlineStr"/>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2582,7 +2798,12 @@
       </c>
       <c r="K44" s="5" t="inlineStr"/>
       <c r="L44" s="4" t="inlineStr"/>
-      <c r="M44" s="4" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2627,7 +2848,12 @@
       </c>
       <c r="K45" s="5" t="inlineStr"/>
       <c r="L45" s="4" t="inlineStr"/>
-      <c r="M45" s="4" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2672,7 +2898,12 @@
       </c>
       <c r="K46" s="5" t="inlineStr"/>
       <c r="L46" s="4" t="inlineStr"/>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>Distinct "cheapest" price intent; keep, link to hub + pricing guide.</t>
         </is>
@@ -2717,7 +2948,12 @@
       </c>
       <c r="K47" s="5" t="inlineStr"/>
       <c r="L47" s="4" t="inlineStr"/>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2762,7 +2998,12 @@
       </c>
       <c r="K48" s="5" t="inlineStr"/>
       <c r="L48" s="4" t="inlineStr"/>
-      <c r="M48" s="4" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2807,7 +3048,12 @@
       </c>
       <c r="K49" s="5" t="inlineStr"/>
       <c r="L49" s="4" t="inlineStr"/>
-      <c r="M49" s="4" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2852,7 +3098,12 @@
       </c>
       <c r="K50" s="5" t="inlineStr"/>
       <c r="L50" s="4" t="inlineStr"/>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2897,7 +3148,12 @@
       </c>
       <c r="K51" s="5" t="inlineStr"/>
       <c r="L51" s="4" t="inlineStr"/>
-      <c r="M51" s="4" t="inlineStr">
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -2942,7 +3198,12 @@
       </c>
       <c r="K52" s="5" t="inlineStr"/>
       <c r="L52" s="4" t="inlineStr"/>
-      <c r="M52" s="4" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -2999,7 +3260,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M53" s="4" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
         <is>
           <t>Fold into canonical roundup; 301.</t>
         </is>
@@ -3044,7 +3310,12 @@
       </c>
       <c r="K54" s="5" t="inlineStr"/>
       <c r="L54" s="4" t="inlineStr"/>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3089,7 +3360,12 @@
       </c>
       <c r="K55" s="5" t="inlineStr"/>
       <c r="L55" s="4" t="inlineStr"/>
-      <c r="M55" s="4" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3134,7 +3410,12 @@
       </c>
       <c r="K56" s="5" t="inlineStr"/>
       <c r="L56" s="4" t="inlineStr"/>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
         <is>
           <t>Distinct how-to; keep as GHL spoke.</t>
         </is>
@@ -3191,7 +3472,12 @@
           <t>MEDIUM - review shared</t>
         </is>
       </c>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
         <is>
           <t>Same intent; merge + 301.</t>
         </is>
@@ -3236,7 +3522,12 @@
       </c>
       <c r="K58" s="5" t="inlineStr"/>
       <c r="L58" s="4" t="inlineStr"/>
-      <c r="M58" s="4" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
         <is>
           <t>Distinct angle; keep as GHL spoke.</t>
         </is>
@@ -3293,7 +3584,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M59" s="4" t="inlineStr">
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
         <is>
           <t>Fold into the new GHL landing page; 301.</t>
         </is>
@@ -3350,7 +3646,12 @@
           <t>MEDIUM - review shared</t>
         </is>
       </c>
-      <c r="M60" s="4" t="inlineStr">
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
         <is>
           <t>Same intent; merge + 301.</t>
         </is>
@@ -3395,7 +3696,12 @@
       </c>
       <c r="K61" s="5" t="inlineStr"/>
       <c r="L61" s="4" t="inlineStr"/>
-      <c r="M61" s="4" t="inlineStr">
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -3440,7 +3746,12 @@
       </c>
       <c r="K62" s="5" t="inlineStr"/>
       <c r="L62" s="4" t="inlineStr"/>
-      <c r="M62" s="4" t="inlineStr">
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3489,7 +3800,12 @@
           <t>SOURCE HAS NO QUERIES - safe to redirect</t>
         </is>
       </c>
-      <c r="M63" s="4" t="inlineStr">
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
         <is>
           <t>Chatbot definitional; 301 to voice.</t>
         </is>
@@ -3534,7 +3850,12 @@
       </c>
       <c r="K64" s="5" t="inlineStr"/>
       <c r="L64" s="4" t="inlineStr"/>
-      <c r="M64" s="4" t="inlineStr">
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="inlineStr">
         <is>
           <t>Distinct cost-to-start intent; keep.</t>
         </is>
@@ -3591,7 +3912,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M65" s="4" t="inlineStr">
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
         <is>
           <t>Same intent; merge + 301.</t>
         </is>
@@ -3636,7 +3962,12 @@
       </c>
       <c r="K66" s="5" t="inlineStr"/>
       <c r="L66" s="4" t="inlineStr"/>
-      <c r="M66" s="4" t="inlineStr">
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3681,7 +4012,12 @@
       </c>
       <c r="K67" s="5" t="inlineStr"/>
       <c r="L67" s="4" t="inlineStr"/>
-      <c r="M67" s="4" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3738,7 +4074,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M68" s="4" t="inlineStr">
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N68" s="4" t="inlineStr">
         <is>
           <t>Chatbot; 301 to voice features checklist.</t>
         </is>
@@ -3783,7 +4124,12 @@
       </c>
       <c r="K69" s="5" t="inlineStr"/>
       <c r="L69" s="4" t="inlineStr"/>
-      <c r="M69" s="4" t="inlineStr">
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3828,7 +4174,12 @@
       </c>
       <c r="K70" s="5" t="inlineStr"/>
       <c r="L70" s="4" t="inlineStr"/>
-      <c r="M70" s="4" t="inlineStr">
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3873,7 +4224,12 @@
       </c>
       <c r="K71" s="5" t="inlineStr"/>
       <c r="L71" s="4" t="inlineStr"/>
-      <c r="M71" s="4" t="inlineStr">
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -3926,7 +4282,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M72" s="4" t="inlineStr">
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="inlineStr">
         <is>
           <t>GSC: 96 queries — too much traffic to redirect. Rewrite to voice framing ("how to start a voice AI agency") and keep the URL as a primary start guide.</t>
         </is>
@@ -3971,7 +4332,12 @@
       </c>
       <c r="K73" s="5" t="inlineStr"/>
       <c r="L73" s="4" t="inlineStr"/>
-      <c r="M73" s="4" t="inlineStr">
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -4016,7 +4382,12 @@
       </c>
       <c r="K74" s="5" t="inlineStr"/>
       <c r="L74" s="4" t="inlineStr"/>
-      <c r="M74" s="4" t="inlineStr">
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4061,7 +4432,12 @@
       </c>
       <c r="K75" s="5" t="inlineStr"/>
       <c r="L75" s="4" t="inlineStr"/>
-      <c r="M75" s="4" t="inlineStr">
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -4106,7 +4482,12 @@
       </c>
       <c r="K76" s="5" t="inlineStr"/>
       <c r="L76" s="4" t="inlineStr"/>
-      <c r="M76" s="4" t="inlineStr">
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4151,7 +4532,12 @@
       </c>
       <c r="K77" s="5" t="inlineStr"/>
       <c r="L77" s="4" t="inlineStr"/>
-      <c r="M77" s="4" t="inlineStr">
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -4196,7 +4582,12 @@
       </c>
       <c r="K78" s="5" t="inlineStr"/>
       <c r="L78" s="4" t="inlineStr"/>
-      <c r="M78" s="4" t="inlineStr">
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N78" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -4241,7 +4632,12 @@
       </c>
       <c r="K79" s="5" t="inlineStr"/>
       <c r="L79" s="4" t="inlineStr"/>
-      <c r="M79" s="4" t="inlineStr">
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -4286,7 +4682,12 @@
       </c>
       <c r="K80" s="5" t="inlineStr"/>
       <c r="L80" s="4" t="inlineStr"/>
-      <c r="M80" s="4" t="inlineStr">
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N80" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4331,7 +4732,12 @@
       </c>
       <c r="K81" s="5" t="inlineStr"/>
       <c r="L81" s="4" t="inlineStr"/>
-      <c r="M81" s="4" t="inlineStr">
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N81" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4388,7 +4794,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M82" s="4" t="inlineStr">
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="inlineStr">
         <is>
           <t>Same intent; merge as a section + 301.</t>
         </is>
@@ -4433,7 +4844,12 @@
       </c>
       <c r="K83" s="5" t="inlineStr"/>
       <c r="L83" s="4" t="inlineStr"/>
-      <c r="M83" s="4" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -4478,7 +4894,12 @@
       </c>
       <c r="K84" s="5" t="inlineStr"/>
       <c r="L84" s="4" t="inlineStr"/>
-      <c r="M84" s="4" t="inlineStr">
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N84" s="4" t="inlineStr">
         <is>
           <t>SERP-validated (keep): ranks #2 for "my ai front desk alternative" — distinct intent from the vs.</t>
         </is>
@@ -4523,7 +4944,12 @@
       </c>
       <c r="K85" s="5" t="inlineStr"/>
       <c r="L85" s="4" t="inlineStr"/>
-      <c r="M85" s="4" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N85" s="4" t="inlineStr">
         <is>
           <t>SERP-validated (keep): distinct white-label angle; differentiate from alternative-2026 (general) and the vs (head-to-head).</t>
         </is>
@@ -4568,7 +4994,12 @@
       </c>
       <c r="K86" s="5" t="inlineStr"/>
       <c r="L86" s="4" t="inlineStr"/>
-      <c r="M86" s="4" t="inlineStr">
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N86" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -4613,7 +5044,12 @@
       </c>
       <c r="K87" s="5" t="inlineStr"/>
       <c r="L87" s="4" t="inlineStr"/>
-      <c r="M87" s="4" t="inlineStr">
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -4658,7 +5094,12 @@
       </c>
       <c r="K88" s="5" t="inlineStr"/>
       <c r="L88" s="4" t="inlineStr"/>
-      <c r="M88" s="4" t="inlineStr">
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N88" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4703,7 +5144,12 @@
       </c>
       <c r="K89" s="5" t="inlineStr"/>
       <c r="L89" s="4" t="inlineStr"/>
-      <c r="M89" s="4" t="inlineStr">
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N89" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4748,7 +5194,12 @@
       </c>
       <c r="K90" s="5" t="inlineStr"/>
       <c r="L90" s="4" t="inlineStr"/>
-      <c r="M90" s="4" t="inlineStr">
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4793,7 +5244,12 @@
       </c>
       <c r="K91" s="5" t="inlineStr"/>
       <c r="L91" s="4" t="inlineStr"/>
-      <c r="M91" s="4" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -4838,7 +5294,12 @@
       </c>
       <c r="K92" s="5" t="inlineStr"/>
       <c r="L92" s="4" t="inlineStr"/>
-      <c r="M92" s="4" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N92" s="4" t="inlineStr">
         <is>
           <t>SERP-validated (keep): owns the converting "retell ai white label" niche (3.35% CTR); distinct intent from the head-to-head vs.</t>
         </is>
@@ -4883,7 +5344,12 @@
       </c>
       <c r="K93" s="5" t="inlineStr"/>
       <c r="L93" s="4" t="inlineStr"/>
-      <c r="M93" s="4" t="inlineStr">
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N93" s="4" t="inlineStr">
         <is>
           <t>SERP-validated (keep): "smith ai alternative" is roundup intent, distinct from the head-to-head vs.</t>
         </is>
@@ -4928,7 +5394,12 @@
       </c>
       <c r="K94" s="5" t="inlineStr"/>
       <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="4" t="inlineStr">
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -4973,7 +5444,12 @@
       </c>
       <c r="K95" s="5" t="inlineStr"/>
       <c r="L95" s="4" t="inlineStr"/>
-      <c r="M95" s="4" t="inlineStr">
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N95" s="4" t="inlineStr">
         <is>
           <t>SERP-validated (keep): distinct agency-angle content; co-ranks only on the brand term. Differentiate from the vs.</t>
         </is>
@@ -5018,7 +5494,12 @@
       </c>
       <c r="K96" s="5" t="inlineStr"/>
       <c r="L96" s="4" t="inlineStr"/>
-      <c r="M96" s="4" t="inlineStr">
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N96" s="4" t="inlineStr">
         <is>
           <t>Canonical head-to-head. synthflow-alternative-for-agencies has distinct content and is KEPT (SERP-validated).</t>
         </is>
@@ -5063,7 +5544,12 @@
       </c>
       <c r="K97" s="5" t="inlineStr"/>
       <c r="L97" s="4" t="inlineStr"/>
-      <c r="M97" s="4" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N97" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5108,7 +5594,12 @@
       </c>
       <c r="K98" s="5" t="inlineStr"/>
       <c r="L98" s="4" t="inlineStr"/>
-      <c r="M98" s="4" t="inlineStr">
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5153,7 +5644,12 @@
       </c>
       <c r="K99" s="5" t="inlineStr"/>
       <c r="L99" s="4" t="inlineStr"/>
-      <c r="M99" s="4" t="inlineStr">
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N99" s="4" t="inlineStr">
         <is>
           <t>Canonical "best white-label voice AI PLATFORMS" roundup (platforms intent). GSC: 130-533 impr on head terms but pos 19-25. best-white-label-ai-receptionist is a SEPARATE winner (receptionist intent) and is NOT merged in.</t>
         </is>
@@ -5198,7 +5694,12 @@
       </c>
       <c r="K100" s="5" t="inlineStr"/>
       <c r="L100" s="4" t="inlineStr"/>
-      <c r="M100" s="4" t="inlineStr">
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N100" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5243,7 +5744,12 @@
       </c>
       <c r="K101" s="5" t="inlineStr"/>
       <c r="L101" s="4" t="inlineStr"/>
-      <c r="M101" s="4" t="inlineStr">
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5288,7 +5794,12 @@
       </c>
       <c r="K102" s="5" t="inlineStr"/>
       <c r="L102" s="4" t="inlineStr"/>
-      <c r="M102" s="4" t="inlineStr">
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N102" s="4" t="inlineStr">
         <is>
           <t>Canonical "GHL native vs Trillet" comparison.</t>
         </is>
@@ -5333,7 +5844,12 @@
       </c>
       <c r="K103" s="5" t="inlineStr"/>
       <c r="L103" s="4" t="inlineStr"/>
-      <c r="M103" s="4" t="inlineStr">
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N103" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5378,7 +5894,12 @@
       </c>
       <c r="K104" s="5" t="inlineStr"/>
       <c r="L104" s="4" t="inlineStr"/>
-      <c r="M104" s="4" t="inlineStr">
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N104" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5423,7 +5944,12 @@
       </c>
       <c r="K105" s="5" t="inlineStr"/>
       <c r="L105" s="4" t="inlineStr"/>
-      <c r="M105" s="4" t="inlineStr">
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N105" s="4" t="inlineStr">
         <is>
           <t>Canonical head-to-head. The two MAFD alternative pages serve different intent and are KEPT (SERP-validated), not merged here.</t>
         </is>
@@ -5468,7 +5994,12 @@
       </c>
       <c r="K106" s="5" t="inlineStr"/>
       <c r="L106" s="4" t="inlineStr"/>
-      <c r="M106" s="4" t="inlineStr">
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N106" s="4" t="inlineStr">
         <is>
           <t>Canonical head-to-head. The Retell/Vapi white-label "alternative" pages own distinct intent and are KEPT (SERP-validated).</t>
         </is>
@@ -5513,7 +6044,12 @@
       </c>
       <c r="K107" s="5" t="inlineStr"/>
       <c r="L107" s="4" t="inlineStr"/>
-      <c r="M107" s="4" t="inlineStr">
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N107" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5558,7 +6094,12 @@
       </c>
       <c r="K108" s="5" t="inlineStr"/>
       <c r="L108" s="4" t="inlineStr"/>
-      <c r="M108" s="4" t="inlineStr">
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N108" s="4" t="inlineStr">
         <is>
           <t>Canonical head-to-head. smith-ai-alternative-2026 owns roundup intent and is KEPT (SERP-validated).</t>
         </is>
@@ -5603,7 +6144,12 @@
       </c>
       <c r="K109" s="5" t="inlineStr"/>
       <c r="L109" s="4" t="inlineStr"/>
-      <c r="M109" s="4" t="inlineStr">
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N109" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5648,7 +6194,12 @@
       </c>
       <c r="K110" s="5" t="inlineStr"/>
       <c r="L110" s="4" t="inlineStr"/>
-      <c r="M110" s="4" t="inlineStr">
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N110" s="4" t="inlineStr">
         <is>
           <t>SERP-validated (keep): ranks p1 (#3) for "vapi alternative for agencies" — roundup intent, distinct from the vs.</t>
         </is>
@@ -5693,7 +6244,12 @@
       </c>
       <c r="K111" s="5" t="inlineStr"/>
       <c r="L111" s="4" t="inlineStr"/>
-      <c r="M111" s="4" t="inlineStr">
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N111" s="4" t="inlineStr">
         <is>
           <t>Distinct compliance angle (the wedge); keep.</t>
         </is>
@@ -5738,7 +6294,12 @@
       </c>
       <c r="K112" s="5" t="inlineStr"/>
       <c r="L112" s="4" t="inlineStr"/>
-      <c r="M112" s="4" t="inlineStr">
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N112" s="4" t="inlineStr">
         <is>
           <t>Distinct: Vapi own WL options; keep.</t>
         </is>
@@ -5783,7 +6344,12 @@
       </c>
       <c r="K113" s="5" t="inlineStr"/>
       <c r="L113" s="4" t="inlineStr"/>
-      <c r="M113" s="4" t="inlineStr">
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N113" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -5828,7 +6394,12 @@
       </c>
       <c r="K114" s="5" t="inlineStr"/>
       <c r="L114" s="4" t="inlineStr"/>
-      <c r="M114" s="4" t="inlineStr">
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N114" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -5873,7 +6444,12 @@
       </c>
       <c r="K115" s="5" t="inlineStr"/>
       <c r="L115" s="4" t="inlineStr"/>
-      <c r="M115" s="4" t="inlineStr">
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N115" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -5918,7 +6494,12 @@
       </c>
       <c r="K116" s="5" t="inlineStr"/>
       <c r="L116" s="4" t="inlineStr"/>
-      <c r="M116" s="4" t="inlineStr">
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N116" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -5963,7 +6544,12 @@
       </c>
       <c r="K117" s="5" t="inlineStr"/>
       <c r="L117" s="4" t="inlineStr"/>
-      <c r="M117" s="4" t="inlineStr">
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N117" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6008,7 +6594,12 @@
       </c>
       <c r="K118" s="5" t="inlineStr"/>
       <c r="L118" s="4" t="inlineStr"/>
-      <c r="M118" s="4" t="inlineStr">
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N118" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6053,7 +6644,12 @@
       </c>
       <c r="K119" s="5" t="inlineStr"/>
       <c r="L119" s="4" t="inlineStr"/>
-      <c r="M119" s="4" t="inlineStr">
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N119" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6098,7 +6694,12 @@
       </c>
       <c r="K120" s="5" t="inlineStr"/>
       <c r="L120" s="4" t="inlineStr"/>
-      <c r="M120" s="4" t="inlineStr">
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N120" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -6135,7 +6736,12 @@
       </c>
       <c r="K121" s="5" t="inlineStr"/>
       <c r="L121" s="4" t="inlineStr"/>
-      <c r="M121" s="4" t="inlineStr">
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N121" s="4" t="inlineStr">
         <is>
           <t>KEEP but sharpen "sell voice, not chat"; the chatbot-&gt;voice converter.</t>
         </is>
@@ -6180,7 +6786,12 @@
       </c>
       <c r="K122" s="5" t="inlineStr"/>
       <c r="L122" s="4" t="inlineStr"/>
-      <c r="M122" s="4" t="inlineStr">
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N122" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -6225,7 +6836,12 @@
       </c>
       <c r="K123" s="5" t="inlineStr"/>
       <c r="L123" s="4" t="inlineStr"/>
-      <c r="M123" s="4" t="inlineStr">
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N123" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -6270,7 +6886,12 @@
       </c>
       <c r="K124" s="5" t="inlineStr"/>
       <c r="L124" s="4" t="inlineStr"/>
-      <c r="M124" s="4" t="inlineStr">
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N124" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -6315,7 +6936,12 @@
       </c>
       <c r="K125" s="5" t="inlineStr"/>
       <c r="L125" s="4" t="inlineStr"/>
-      <c r="M125" s="4" t="inlineStr">
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N125" s="4" t="inlineStr">
         <is>
           <t>Distinct ROI tool; keep.</t>
         </is>
@@ -6364,7 +6990,12 @@
           <t>SOURCE HAS NO QUERIES - safe to redirect</t>
         </is>
       </c>
-      <c r="M126" s="4" t="inlineStr">
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N126" s="4" t="inlineStr">
         <is>
           <t>Merge + 301.</t>
         </is>
@@ -6409,7 +7040,12 @@
       </c>
       <c r="K127" s="5" t="inlineStr"/>
       <c r="L127" s="4" t="inlineStr"/>
-      <c r="M127" s="4" t="inlineStr">
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N127" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -6446,7 +7082,12 @@
       </c>
       <c r="K128" s="5" t="inlineStr"/>
       <c r="L128" s="4" t="inlineStr"/>
-      <c r="M128" s="4" t="inlineStr">
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N128" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -6491,7 +7132,12 @@
       </c>
       <c r="K129" s="5" t="inlineStr"/>
       <c r="L129" s="4" t="inlineStr"/>
-      <c r="M129" s="4" t="inlineStr">
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N129" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6536,7 +7182,12 @@
       </c>
       <c r="K130" s="5" t="inlineStr"/>
       <c r="L130" s="4" t="inlineStr"/>
-      <c r="M130" s="4" t="inlineStr">
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N130" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6581,7 +7232,12 @@
       </c>
       <c r="K131" s="5" t="inlineStr"/>
       <c r="L131" s="4" t="inlineStr"/>
-      <c r="M131" s="4" t="inlineStr">
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N131" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6626,7 +7282,12 @@
       </c>
       <c r="K132" s="5" t="inlineStr"/>
       <c r="L132" s="4" t="inlineStr"/>
-      <c r="M132" s="4" t="inlineStr">
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N132" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6671,7 +7332,12 @@
       </c>
       <c r="K133" s="5" t="inlineStr"/>
       <c r="L133" s="4" t="inlineStr"/>
-      <c r="M133" s="4" t="inlineStr">
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N133" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6716,7 +7382,12 @@
       </c>
       <c r="K134" s="5" t="inlineStr"/>
       <c r="L134" s="4" t="inlineStr"/>
-      <c r="M134" s="4" t="inlineStr">
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N134" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6761,7 +7432,12 @@
       </c>
       <c r="K135" s="5" t="inlineStr"/>
       <c r="L135" s="4" t="inlineStr"/>
-      <c r="M135" s="4" t="inlineStr">
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N135" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6806,7 +7482,12 @@
       </c>
       <c r="K136" s="5" t="inlineStr"/>
       <c r="L136" s="4" t="inlineStr"/>
-      <c r="M136" s="4" t="inlineStr">
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N136" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6851,7 +7532,12 @@
       </c>
       <c r="K137" s="5" t="inlineStr"/>
       <c r="L137" s="4" t="inlineStr"/>
-      <c r="M137" s="4" t="inlineStr">
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N137" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6896,7 +7582,12 @@
       </c>
       <c r="K138" s="5" t="inlineStr"/>
       <c r="L138" s="4" t="inlineStr"/>
-      <c r="M138" s="4" t="inlineStr">
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N138" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -6941,7 +7632,12 @@
       </c>
       <c r="K139" s="5" t="inlineStr"/>
       <c r="L139" s="4" t="inlineStr"/>
-      <c r="M139" s="4" t="inlineStr">
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N139" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -6986,7 +7682,12 @@
       </c>
       <c r="K140" s="5" t="inlineStr"/>
       <c r="L140" s="4" t="inlineStr"/>
-      <c r="M140" s="4" t="inlineStr">
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N140" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -7031,7 +7732,12 @@
       </c>
       <c r="K141" s="5" t="inlineStr"/>
       <c r="L141" s="4" t="inlineStr"/>
-      <c r="M141" s="4" t="inlineStr">
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N141" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -7076,7 +7782,12 @@
       </c>
       <c r="K142" s="5" t="inlineStr"/>
       <c r="L142" s="4" t="inlineStr"/>
-      <c r="M142" s="4" t="inlineStr">
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N142" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -7121,7 +7832,12 @@
       </c>
       <c r="K143" s="5" t="inlineStr"/>
       <c r="L143" s="4" t="inlineStr"/>
-      <c r="M143" s="4" t="inlineStr">
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N143" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -7166,7 +7882,12 @@
       </c>
       <c r="K144" s="5" t="inlineStr"/>
       <c r="L144" s="4" t="inlineStr"/>
-      <c r="M144" s="4" t="inlineStr">
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N144" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -7223,7 +7944,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M145" s="4" t="inlineStr">
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N145" s="4" t="inlineStr">
         <is>
           <t>Merge + 301.</t>
         </is>
@@ -7276,7 +8002,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M146" s="4" t="inlineStr">
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N146" s="4" t="inlineStr">
         <is>
           <t>GSC-validated survivor: 75 queries vs 21 on the alternative. Canonical voice-vs-text post.</t>
         </is>
@@ -7321,7 +8052,12 @@
       </c>
       <c r="K147" s="5" t="inlineStr"/>
       <c r="L147" s="4" t="inlineStr"/>
-      <c r="M147" s="4" t="inlineStr">
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N147" s="4" t="inlineStr">
         <is>
           <t>Canonical WL-pricing GUIDE. 46k impressions @0.06% CTR — rewrite title/meta/snippet, add table + CTA to /whitelabel/pricing.</t>
         </is>
@@ -7366,7 +8102,12 @@
       </c>
       <c r="K148" s="5" t="inlineStr"/>
       <c r="L148" s="4" t="inlineStr"/>
-      <c r="M148" s="4" t="inlineStr">
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N148" s="4" t="inlineStr">
         <is>
           <t>Canonical wrapper-vs-native (the "we own the stack" differentiator).</t>
         </is>
@@ -7415,7 +8156,12 @@
       </c>
       <c r="K149" s="5" t="inlineStr"/>
       <c r="L149" s="4" t="inlineStr"/>
-      <c r="M149" s="4" t="inlineStr">
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N149" s="4" t="inlineStr">
         <is>
           <t>Fewer queries (21 vs 75); merge into the stronger page + 301.</t>
         </is>
@@ -7460,7 +8206,12 @@
       </c>
       <c r="K150" s="5" t="inlineStr"/>
       <c r="L150" s="4" t="inlineStr"/>
-      <c r="M150" s="4" t="inlineStr">
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N150" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -7505,7 +8256,12 @@
       </c>
       <c r="K151" s="5" t="inlineStr"/>
       <c r="L151" s="4" t="inlineStr"/>
-      <c r="M151" s="4" t="inlineStr">
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N151" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -7550,7 +8306,12 @@
       </c>
       <c r="K152" s="5" t="inlineStr"/>
       <c r="L152" s="4" t="inlineStr"/>
-      <c r="M152" s="4" t="inlineStr">
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N152" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -7595,7 +8356,12 @@
       </c>
       <c r="K153" s="5" t="inlineStr"/>
       <c r="L153" s="4" t="inlineStr"/>
-      <c r="M153" s="4" t="inlineStr">
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N153" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -7640,7 +8406,12 @@
       </c>
       <c r="K154" s="5" t="inlineStr"/>
       <c r="L154" s="4" t="inlineStr"/>
-      <c r="M154" s="4" t="inlineStr">
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N154" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -7697,7 +8468,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M155" s="4" t="inlineStr">
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N155" s="4" t="inlineStr">
         <is>
           <t>Chatbot definitional; 301 to voice.</t>
         </is>
@@ -7742,7 +8518,12 @@
       </c>
       <c r="K156" s="5" t="inlineStr"/>
       <c r="L156" s="4" t="inlineStr"/>
-      <c r="M156" s="4" t="inlineStr">
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N156" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -7787,7 +8568,12 @@
       </c>
       <c r="K157" s="5" t="inlineStr"/>
       <c r="L157" s="4" t="inlineStr"/>
-      <c r="M157" s="4" t="inlineStr">
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N157" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -7832,7 +8618,12 @@
       </c>
       <c r="K158" s="5" t="inlineStr"/>
       <c r="L158" s="4" t="inlineStr"/>
-      <c r="M158" s="4" t="inlineStr">
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N158" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -7877,7 +8668,12 @@
       </c>
       <c r="K159" s="5" t="inlineStr"/>
       <c r="L159" s="4" t="inlineStr"/>
-      <c r="M159" s="4" t="inlineStr">
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N159" s="4" t="inlineStr">
         <is>
           <t>Keep as integrations spoke; link up to /integrations hub.</t>
         </is>
@@ -7934,7 +8730,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M160" s="4" t="inlineStr">
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N160" s="4" t="inlineStr">
         <is>
           <t>Chatbot-framed; 301 to voice pricing guide.</t>
         </is>
@@ -7991,7 +8792,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M161" s="4" t="inlineStr">
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N161" s="4" t="inlineStr">
         <is>
           <t>Merge tool into voice ROI model; 301.</t>
         </is>
@@ -8036,7 +8842,12 @@
       </c>
       <c r="K162" s="5" t="inlineStr"/>
       <c r="L162" s="4" t="inlineStr"/>
-      <c r="M162" s="4" t="inlineStr">
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N162" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8081,7 +8892,12 @@
       </c>
       <c r="K163" s="5" t="inlineStr"/>
       <c r="L163" s="4" t="inlineStr"/>
-      <c r="M163" s="4" t="inlineStr">
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N163" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8126,7 +8942,12 @@
       </c>
       <c r="K164" s="5" t="inlineStr"/>
       <c r="L164" s="4" t="inlineStr"/>
-      <c r="M164" s="4" t="inlineStr">
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N164" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -8171,7 +8992,12 @@
       </c>
       <c r="K165" s="5" t="inlineStr"/>
       <c r="L165" s="4" t="inlineStr"/>
-      <c r="M165" s="4" t="inlineStr">
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N165" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -8216,7 +9042,12 @@
       </c>
       <c r="K166" s="5" t="inlineStr"/>
       <c r="L166" s="4" t="inlineStr"/>
-      <c r="M166" s="4" t="inlineStr">
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N166" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -8261,7 +9092,12 @@
       </c>
       <c r="K167" s="5" t="inlineStr"/>
       <c r="L167" s="4" t="inlineStr"/>
-      <c r="M167" s="4" t="inlineStr">
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N167" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -8306,7 +9142,12 @@
       </c>
       <c r="K168" s="5" t="inlineStr"/>
       <c r="L168" s="4" t="inlineStr"/>
-      <c r="M168" s="4" t="inlineStr">
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N168" s="4" t="inlineStr">
         <is>
           <t>Keep. Link up to /whitelabel + cross-link its /receptionist/industries counterpart (differentiate reseller vs end-customer).</t>
         </is>
@@ -8351,7 +9192,12 @@
       </c>
       <c r="K169" s="5" t="inlineStr"/>
       <c r="L169" s="4" t="inlineStr"/>
-      <c r="M169" s="4" t="inlineStr">
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N169" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8408,7 +9254,12 @@
           <t>MEDIUM - review shared</t>
         </is>
       </c>
-      <c r="M170" s="4" t="inlineStr">
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N170" s="4" t="inlineStr">
         <is>
           <t>Near-duplicate; merge + 301.</t>
         </is>
@@ -8453,7 +9304,12 @@
       </c>
       <c r="K171" s="5" t="inlineStr"/>
       <c r="L171" s="4" t="inlineStr"/>
-      <c r="M171" s="4" t="inlineStr">
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N171" s="4" t="inlineStr">
         <is>
           <t>Canonical profit-margins post.</t>
         </is>
@@ -8498,7 +9354,12 @@
       </c>
       <c r="K172" s="5" t="inlineStr"/>
       <c r="L172" s="4" t="inlineStr"/>
-      <c r="M172" s="4" t="inlineStr">
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N172" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -8543,7 +9404,12 @@
       </c>
       <c r="K173" s="5" t="inlineStr"/>
       <c r="L173" s="4" t="inlineStr"/>
-      <c r="M173" s="4" t="inlineStr">
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N173" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8588,7 +9454,12 @@
       </c>
       <c r="K174" s="5" t="inlineStr"/>
       <c r="L174" s="4" t="inlineStr"/>
-      <c r="M174" s="4" t="inlineStr">
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N174" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8633,7 +9504,12 @@
       </c>
       <c r="K175" s="5" t="inlineStr"/>
       <c r="L175" s="4" t="inlineStr"/>
-      <c r="M175" s="4" t="inlineStr">
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N175" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8678,7 +9554,12 @@
       </c>
       <c r="K176" s="5" t="inlineStr"/>
       <c r="L176" s="4" t="inlineStr"/>
-      <c r="M176" s="4" t="inlineStr">
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N176" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8723,7 +9604,12 @@
       </c>
       <c r="K177" s="5" t="inlineStr"/>
       <c r="L177" s="4" t="inlineStr"/>
-      <c r="M177" s="4" t="inlineStr">
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N177" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8768,7 +9654,12 @@
       </c>
       <c r="K178" s="5" t="inlineStr"/>
       <c r="L178" s="4" t="inlineStr"/>
-      <c r="M178" s="4" t="inlineStr">
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N178" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8825,7 +9716,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M179" s="4" t="inlineStr">
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N179" s="4" t="inlineStr">
         <is>
           <t>Off-topic (chatgpt); 301 to hub.</t>
         </is>
@@ -8870,7 +9766,12 @@
       </c>
       <c r="K180" s="5" t="inlineStr"/>
       <c r="L180" s="4" t="inlineStr"/>
-      <c r="M180" s="4" t="inlineStr">
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N180" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8915,7 +9816,12 @@
       </c>
       <c r="K181" s="5" t="inlineStr"/>
       <c r="L181" s="4" t="inlineStr"/>
-      <c r="M181" s="4" t="inlineStr">
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N181" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -8960,7 +9866,12 @@
       </c>
       <c r="K182" s="5" t="inlineStr"/>
       <c r="L182" s="4" t="inlineStr"/>
-      <c r="M182" s="4" t="inlineStr">
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N182" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -9005,7 +9916,12 @@
       </c>
       <c r="K183" s="5" t="inlineStr"/>
       <c r="L183" s="4" t="inlineStr"/>
-      <c r="M183" s="4" t="inlineStr">
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N183" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -9062,7 +9978,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M184" s="4" t="inlineStr">
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N184" s="4" t="inlineStr">
         <is>
           <t>Merge + 301. SURVIVOR REVIEW: this source has 13 queries vs 2 on the target — confirm which URL survives before 301.</t>
         </is>
@@ -9119,7 +10040,12 @@
           <t>LOW - keep both</t>
         </is>
       </c>
-      <c r="M185" s="4" t="inlineStr">
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N185" s="4" t="inlineStr">
         <is>
           <t>Chatbot build-vs-buy; 301 to canonical build-vs-buy.</t>
         </is>
@@ -9164,7 +10090,12 @@
       </c>
       <c r="K186" s="5" t="inlineStr"/>
       <c r="L186" s="4" t="inlineStr"/>
-      <c r="M186" s="4" t="inlineStr">
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N186" s="4" t="inlineStr">
         <is>
           <t>Distinct intent — keep as spoke; add hub link + related-in-cluster module.</t>
         </is>
@@ -9209,7 +10140,12 @@
       </c>
       <c r="K187" s="5" t="inlineStr"/>
       <c r="L187" s="4" t="inlineStr"/>
-      <c r="M187" s="4" t="inlineStr">
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N187" s="4" t="inlineStr">
         <is>
           <t>Keep. Organise under the Academy hub; link to /partners application.</t>
         </is>
@@ -9254,7 +10190,12 @@
       </c>
       <c r="K188" s="5" t="inlineStr"/>
       <c r="L188" s="4" t="inlineStr"/>
-      <c r="M188" s="4" t="inlineStr">
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N188" s="4" t="inlineStr">
         <is>
           <t>Keep (single competitor/angle). Ensure comparison table, current pricing, compliance wedge, CTA.</t>
         </is>
@@ -9299,7 +10240,12 @@
       </c>
       <c r="K189" s="5" t="inlineStr"/>
       <c r="L189" s="4" t="inlineStr"/>
-      <c r="M189" s="4" t="inlineStr">
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N189" s="4" t="inlineStr">
         <is>
           <t>Revamp under the program hub.</t>
         </is>
@@ -9344,7 +10290,12 @@
       </c>
       <c r="K190" s="5" t="inlineStr"/>
       <c r="L190" s="4" t="inlineStr"/>
-      <c r="M190" s="4" t="inlineStr">
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N190" s="4" t="inlineStr">
         <is>
           <t>Revamp; link from voice-ai-agency-referral-program.</t>
         </is>
@@ -9389,7 +10340,12 @@
       </c>
       <c r="K191" s="5" t="inlineStr"/>
       <c r="L191" s="4" t="inlineStr"/>
-      <c r="M191" s="4" t="inlineStr">
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="N191" s="4" t="inlineStr">
         <is>
           <t>Revamp under the program hub; wire Academy posts to it.</t>
         </is>
@@ -9438,14 +10394,19 @@
       </c>
       <c r="K192" s="5" t="inlineStr"/>
       <c r="L192" s="4" t="inlineStr"/>
-      <c r="M192" s="4" t="inlineStr">
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>308 -&gt; https://trillet.ai/whitelabel</t>
+        </is>
+      </c>
+      <c r="N192" s="4" t="inlineStr">
         <is>
           <t>ALREADY 308-redirected to /whitelabel (permanent; passes signal like a 301) - NO ACTION. Its historical head-term impressions in the 16-mo data will consolidate into /whitelabel as Google reprocesses (same as the apex/www fix). Only verify no internal links still point to /agency.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M192"/>
+  <autoFilter ref="A1:N192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
